--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$102</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$104</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$92</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4780,7 +4780,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4908,7 +4908,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.1, "op_wape_pct": 99.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 1894.0, "rev_act": 2052.74, "op_pred": 77.15, "op_act": -0.39}, {"q": "2025Q4", "rev_pred": 2042.29, "rev_act": 1871.9, "op_pred": 83.19, "op_act": -5.64}, {"q": "2026Q1", "rev_pred": 1934.7, "rev_act": 1966.68, "op_pred": 78.8, "op_act": 132.39}, {"q": "2026Q2", "rev_pred": 2071.1, "rev_act": 2290.92, "op_pred": 84.36, "op_act": 179.9}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.1, "op_wape_pct": 99.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 1894.0, "rev_act": 2052.74, "op_pred": 77.15, "op_act": -0.39}, {"q": "2025Q4", "rev_pred": 2042.29, "rev_act": 1871.9, "op_pred": 83.19, "op_act": -5.64}, {"q": "2026Q1", "rev_pred": 1934.7, "rev_act": 1966.68, "op_pred": 78.8, "op_act": 132.39}, {"q": "2026Q2", "rev_pred": 2071.1, "rev_act": 2290.92, "op_pred": 84.36, "op_act": 179.9}]}</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>-54.9</v>
+        <v>-54.91</v>
       </c>
       <c r="AG25" s="29" t="n">
         <v>-54.87</v>
@@ -7566,7 +7566,7 @@
         <v>-55.01</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>-54.96</v>
+        <v>-54.97</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -8006,13 +8006,13 @@
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.27027</v>
+        <v>0.270588</v>
       </c>
       <c r="AG28" s="24" t="n">
         <v>0.270098</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.269653</v>
+        <v>0.269899</v>
       </c>
       <c r="AI28" s="24" t="n">
         <v>0.269294</v>
@@ -8031,7 +8031,7 @@
         <v>0.270417</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.270665</v>
+        <v>0.269044</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8763,13 +8763,13 @@
         <v>0</v>
       </c>
       <c r="AG34" s="29" t="n">
-        <v>33.99</v>
+        <v>34</v>
       </c>
       <c r="AH34" s="29" t="n">
         <v>-0</v>
       </c>
       <c r="AI34" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AJ34" s="30" t="n"/>
       <c r="AK34" s="29" t="n">
@@ -8779,7 +8779,7 @@
         <v>34</v>
       </c>
       <c r="AM34" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AN34" s="29" t="n">
         <v>0</v>
@@ -8881,23 +8881,23 @@
         <v/>
       </c>
       <c r="AC35" s="29" t="n">
-        <v>-0.0023</v>
+        <v>0.0077</v>
       </c>
       <c r="AD35" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AE35" s="30" t="n"/>
       <c r="AF35" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AG35" s="29" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="AH35" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="AG35" s="29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH35" s="29" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="AI35" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ35" s="30" t="n"/>
       <c r="AK35" s="29" t="n">
@@ -8907,10 +8907,10 @@
         <v>33.99</v>
       </c>
       <c r="AM35" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AN35" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO35" s="30" t="n"/>
     </row>
@@ -9150,7 +9150,7 @@
         <v>0.00471</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>-0.001752</v>
+        <v>-0.00175</v>
       </c>
       <c r="AI37" s="24" t="n">
         <v>-0.000975</v>
@@ -9163,7 +9163,7 @@
         <v>0.004673</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>-0.001764</v>
+        <v>-0.001762</v>
       </c>
       <c r="AN37" s="24" t="n">
         <v>-0.0009879999999999999</v>
@@ -9275,23 +9275,23 @@
         <v>0.003538</v>
       </c>
       <c r="AG38" s="24" t="n">
-        <v>-0.012133</v>
+        <v>-0.012139</v>
       </c>
       <c r="AH38" s="24" t="n">
         <v>0.004587</v>
       </c>
       <c r="AI38" s="24" t="n">
-        <v>0.00254</v>
+        <v>0.002546</v>
       </c>
       <c r="AJ38" s="25" t="n"/>
       <c r="AK38" s="24" t="n">
-        <v>0.003618</v>
+        <v>0.003612</v>
       </c>
       <c r="AL38" s="24" t="n">
         <v>-0.012066</v>
       </c>
       <c r="AM38" s="24" t="n">
-        <v>0.004633</v>
+        <v>0.004628</v>
       </c>
       <c r="AN38" s="24" t="n">
         <v>0.002578</v>
@@ -10861,7 +10861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO102"/>
+  <dimension ref="A1:AO104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11109,7 +11109,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -13237,16 +13237,16 @@
         <v>426221.11</v>
       </c>
       <c r="X24" s="18" t="n">
-        <v>365935.83</v>
+        <v>315836.81</v>
       </c>
       <c r="Y24" s="18" t="n">
-        <v>346199.51</v>
+        <v>304530.9</v>
       </c>
       <c r="Z24" s="34" t="n">
-        <v>346199.51</v>
+        <v>304530.9</v>
       </c>
       <c r="AA24" s="18" t="n">
-        <v>367765.36</v>
+        <v>331099.6</v>
       </c>
       <c r="AB24" s="19" t="n">
         <v>392878.52</v>
@@ -13331,18 +13331,7 @@
       <c r="W25" s="18" t="n">
         <v>426221.11</v>
       </c>
-      <c r="X25" s="18" t="n">
-        <v>365935.83</v>
-      </c>
-      <c r="Y25" s="18" t="n">
-        <v>346199.51</v>
-      </c>
-      <c r="Z25" s="34" t="n">
-        <v>346199.51</v>
-      </c>
-      <c r="AA25" s="18" t="n">
-        <v>367765.36</v>
-      </c>
+      <c r="Z25" s="9" t="n"/>
       <c r="AB25" s="19" t="n">
         <v>392878.52</v>
       </c>
@@ -13939,7 +13928,12 @@
       <c r="S32" s="18" t="n">
         <v>97705.83</v>
       </c>
-      <c r="U32" s="9" t="n"/>
+      <c r="T32" s="18" t="n">
+        <v>91283.42</v>
+      </c>
+      <c r="U32" s="34" t="n">
+        <v>91283.42</v>
+      </c>
       <c r="V32" s="18" t="n">
         <v>127659.57</v>
       </c>
@@ -15308,16 +15302,16 @@
         <v>513858.49</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>391077.77</v>
+        <v>502328.45</v>
       </c>
       <c r="U47" s="34" t="n">
-        <v>391077.77</v>
+        <v>502328.45</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>520476.01</v>
+        <v>560406.33</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>533160.11</v>
+        <v>573096.8</v>
       </c>
       <c r="X47" s="18" t="n">
         <v>537102.49</v>
@@ -15329,7 +15323,7 @@
         <v>351228.45</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>550421.25</v>
+        <v>550361.38</v>
       </c>
       <c r="AB47" s="19" t="n">
         <v>608041.83</v>
@@ -15403,16 +15397,16 @@
         <v>422790.45</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>303621.01</v>
+        <v>414871.69</v>
       </c>
       <c r="U48" s="34" t="n">
-        <v>303621.01</v>
+        <v>414871.69</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>399346.21</v>
+        <v>439276.53</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>418272.43</v>
+        <v>458209.12</v>
       </c>
       <c r="X48" s="18" t="n">
         <v>400932.57</v>
@@ -15424,7 +15418,7 @@
         <v>244007.13</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>415448.22</v>
+        <v>415388.35</v>
       </c>
       <c r="AB48" s="19" t="n">
         <v>455719.13</v>
@@ -15768,28 +15762,26 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>사채</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
       <c r="K55" s="9" t="n"/>
       <c r="P55" s="9" t="n"/>
-      <c r="U55" s="9" t="n"/>
-      <c r="X55" s="18" t="n">
-        <v>4641.34</v>
-      </c>
-      <c r="Y55" s="18" t="n">
-        <v>5028.94</v>
-      </c>
-      <c r="Z55" s="34" t="n">
-        <v>5028.94</v>
-      </c>
-      <c r="AA55" s="18" t="n">
-        <v>5349.24</v>
-      </c>
-      <c r="AB55" s="19" t="n">
-        <v>11170.58</v>
-      </c>
+      <c r="T55" s="18" t="n">
+        <v>19967.26</v>
+      </c>
+      <c r="U55" s="34" t="n">
+        <v>19967.26</v>
+      </c>
+      <c r="V55" s="18" t="n">
+        <v>39930.32</v>
+      </c>
+      <c r="W55" s="18" t="n">
+        <v>39936.69</v>
+      </c>
+      <c r="Z55" s="9" t="n"/>
+      <c r="AB55" s="5" t="n"/>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
       <c r="AE55" s="11" t="n"/>
@@ -15810,78 +15802,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E56" s="18" t="n">
-        <v>145112.78</v>
+          <t>장기금융부채(face)</t>
+        </is>
       </c>
       <c r="F56" s="9" t="n"/>
-      <c r="G56" s="18" t="n">
-        <v>173504.74</v>
-      </c>
-      <c r="H56" s="18" t="n">
-        <v>169743.96</v>
-      </c>
-      <c r="I56" s="18" t="n">
-        <v>177648.71</v>
-      </c>
-      <c r="J56" s="18" t="n">
-        <v>208034.6</v>
-      </c>
-      <c r="K56" s="34" t="n">
-        <v>728932.01</v>
-      </c>
-      <c r="L56" s="18" t="n">
-        <v>210598.27</v>
-      </c>
-      <c r="M56" s="18" t="n">
-        <v>214308.71</v>
-      </c>
-      <c r="N56" s="18" t="n">
-        <v>211036.44</v>
-      </c>
-      <c r="O56" s="18" t="n">
-        <v>220949.28</v>
-      </c>
-      <c r="P56" s="34" t="n">
-        <v>856892.7</v>
-      </c>
-      <c r="Q56" s="18" t="n">
-        <v>209293.48</v>
-      </c>
-      <c r="R56" s="18" t="n">
-        <v>189474.93</v>
-      </c>
-      <c r="S56" s="18" t="n">
-        <v>193709.01</v>
-      </c>
-      <c r="T56" s="18" t="n">
-        <v>208874.59</v>
-      </c>
-      <c r="U56" s="34" t="n">
-        <v>801352.01</v>
-      </c>
-      <c r="V56" s="18" t="n">
-        <v>197870.76</v>
-      </c>
-      <c r="W56" s="18" t="n">
-        <v>211821.39</v>
-      </c>
+      <c r="K56" s="9" t="n"/>
+      <c r="P56" s="9" t="n"/>
+      <c r="U56" s="9" t="n"/>
       <c r="X56" s="18" t="n">
-        <v>205273.93</v>
+        <v>4641.34</v>
       </c>
       <c r="Y56" s="18" t="n">
-        <v>187189.93</v>
+        <v>5028.94</v>
       </c>
       <c r="Z56" s="34" t="n">
-        <v>802156.01</v>
+        <v>5028.94</v>
       </c>
       <c r="AA56" s="18" t="n">
-        <v>196667.64</v>
+        <v>5349.24</v>
       </c>
       <c r="AB56" s="19" t="n">
-        <v>229092.31</v>
+        <v>11170.58</v>
       </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -15903,79 +15844,26 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>매출원가</t>
-        </is>
-      </c>
-      <c r="E57" s="18" t="n">
-        <v>121131.79</v>
+          <t>유동성장기부채</t>
+        </is>
       </c>
       <c r="F57" s="9" t="n"/>
-      <c r="G57" s="18" t="n">
-        <v>146525.21</v>
-      </c>
-      <c r="H57" s="18" t="n">
-        <v>141725.6</v>
-      </c>
-      <c r="I57" s="18" t="n">
-        <v>150135.15</v>
-      </c>
-      <c r="J57" s="18" t="n">
-        <v>180200.25</v>
-      </c>
-      <c r="K57" s="34" t="n">
-        <v>618586.21</v>
-      </c>
-      <c r="L57" s="18" t="n">
-        <v>174858.2</v>
-      </c>
-      <c r="M57" s="18" t="n">
-        <v>173686.92</v>
-      </c>
-      <c r="N57" s="18" t="n">
-        <v>169138.32</v>
-      </c>
-      <c r="O57" s="18" t="n">
-        <v>181141.91</v>
-      </c>
-      <c r="P57" s="34" t="n">
-        <v>698825.35</v>
-      </c>
-      <c r="Q57" s="18" t="n">
-        <v>173763.71</v>
-      </c>
-      <c r="R57" s="18" t="n">
-        <v>158776.44</v>
-      </c>
-      <c r="S57" s="18" t="n">
-        <v>162033.55</v>
-      </c>
-      <c r="T57" s="18" t="n">
-        <v>180023.28</v>
-      </c>
-      <c r="U57" s="34" t="n">
-        <v>674596.98</v>
-      </c>
-      <c r="V57" s="18" t="n">
-        <v>165223.43</v>
-      </c>
-      <c r="W57" s="18" t="n">
-        <v>179705.97</v>
-      </c>
+      <c r="K57" s="9" t="n"/>
+      <c r="P57" s="9" t="n"/>
+      <c r="U57" s="9" t="n"/>
       <c r="X57" s="18" t="n">
-        <v>173319.08</v>
+        <v>50099.02</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>161691.22</v>
+        <v>41668.61</v>
       </c>
       <c r="Z57" s="34" t="n">
-        <v>679939.7</v>
+        <v>41668.61</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>158096.34</v>
-      </c>
-      <c r="AB57" s="19" t="n">
-        <v>182845.31</v>
-      </c>
+        <v>36605.89</v>
+      </c>
+      <c r="AB57" s="5" t="n"/>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
       <c r="AE57" s="11" t="n"/>
@@ -15996,78 +15884,78 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="E58" s="18" t="n">
-        <v>23980.99</v>
+        <v>145112.78</v>
       </c>
       <c r="F58" s="9" t="n"/>
       <c r="G58" s="18" t="n">
-        <v>26979.53</v>
+        <v>173504.74</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>28018.36</v>
+        <v>169743.96</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>27513.56</v>
+        <v>177648.71</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>27834.34</v>
+        <v>208034.6</v>
       </c>
       <c r="K58" s="34" t="n">
-        <v>110345.79</v>
+        <v>728932.01</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>35740.07</v>
+        <v>210598.27</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>40621.79</v>
+        <v>214308.71</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>41898.12</v>
+        <v>211036.44</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>39807.37</v>
+        <v>220949.28</v>
       </c>
       <c r="P58" s="34" t="n">
-        <v>158067.35</v>
+        <v>856892.7</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>35529.77</v>
+        <v>209293.48</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>30698.49</v>
+        <v>189474.93</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>31675.47</v>
+        <v>193709.01</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>28851.31</v>
+        <v>208874.59</v>
       </c>
       <c r="U58" s="34" t="n">
-        <v>126755.04</v>
+        <v>801352.01</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>32647.33</v>
+        <v>197870.76</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>32115.42</v>
+        <v>211821.39</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>31954.86</v>
+        <v>205273.93</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>25498.71</v>
+        <v>187189.93</v>
       </c>
       <c r="Z58" s="34" t="n">
-        <v>122216.32</v>
+        <v>802156.01</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>38571.3</v>
+        <v>196667.64</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>46247.01</v>
+        <v>229092.31</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -16089,78 +15977,78 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>20353.34</v>
+        <v>121131.79</v>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="G59" s="18" t="n">
-        <v>14958.49</v>
+        <v>146525.21</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>18160.71</v>
+        <v>141725.6</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>21062.07</v>
+        <v>150135.15</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>22225.06</v>
+        <v>180200.25</v>
       </c>
       <c r="K59" s="34" t="n">
-        <v>76406.33</v>
+        <v>618586.21</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>19988.67</v>
+        <v>174858.2</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>22359.31</v>
+        <v>173686.92</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>22962.35</v>
+        <v>169138.32</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>26174.94</v>
+        <v>181141.91</v>
       </c>
       <c r="P59" s="34" t="n">
-        <v>91485.27</v>
+        <v>698825.35</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>21887.39</v>
+        <v>173763.71</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>22025.67</v>
+        <v>158776.44</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>25910.01</v>
+        <v>162033.55</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>23883.76</v>
+        <v>180023.28</v>
       </c>
       <c r="U59" s="34" t="n">
-        <v>93706.83</v>
+        <v>674596.98</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>25585.14</v>
+        <v>165223.43</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>28076.88</v>
+        <v>179705.97</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>31994.23</v>
+        <v>173319.08</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>26062.67</v>
+        <v>161691.22</v>
       </c>
       <c r="Z59" s="34" t="n">
-        <v>111718.92</v>
+        <v>679939.7</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>25332.05</v>
+        <v>158096.34</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>28256.8</v>
+        <v>182845.31</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -16182,78 +16070,78 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>3627.65</v>
+        <v>23980.99</v>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="G60" s="18" t="n">
-        <v>12021.04</v>
+        <v>26979.53</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>9857.65</v>
+        <v>28018.36</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>6451.49</v>
+        <v>27513.56</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>5609.28</v>
+        <v>27834.34</v>
       </c>
       <c r="K60" s="34" t="n">
-        <v>33939.46</v>
+        <v>110345.79</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>15751.4</v>
+        <v>35740.07</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>18262.48</v>
+        <v>40621.79</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>18935.77</v>
+        <v>41898.12</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>13632.43</v>
+        <v>39807.37</v>
       </c>
       <c r="P60" s="34" t="n">
-        <v>66582.08</v>
+        <v>158067.35</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>13642.38</v>
+        <v>35529.77</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>8672.82</v>
+        <v>30698.49</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>5765.46</v>
+        <v>31675.47</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>4967.55</v>
+        <v>28851.31</v>
       </c>
       <c r="U60" s="34" t="n">
-        <v>33048.21</v>
+        <v>126755.04</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>7062.19</v>
+        <v>32647.33</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>4038.54</v>
+        <v>32115.42</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>-39.37</v>
+        <v>31954.86</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>-563.96</v>
+        <v>25498.71</v>
       </c>
       <c r="Z60" s="34" t="n">
-        <v>10497.4</v>
+        <v>122216.32</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>13239.25</v>
+        <v>38571.3</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>17990.21</v>
+        <v>46247.01</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -16275,78 +16163,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>583.74</v>
+        <v>20353.34</v>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="18" t="n">
-        <v>593.9400000000001</v>
+        <v>14958.49</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>478.79</v>
+        <v>18160.71</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>620.9400000000001</v>
+        <v>21062.07</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>963.04</v>
+        <v>22225.06</v>
       </c>
       <c r="K61" s="34" t="n">
-        <v>2656.71</v>
+        <v>76406.33</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>852.84</v>
+        <v>19988.67</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>828.47</v>
+        <v>22359.31</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>811.14</v>
+        <v>22962.35</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>644.24</v>
+        <v>26174.94</v>
       </c>
       <c r="P61" s="34" t="n">
-        <v>3136.69</v>
+        <v>91485.27</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>967.14</v>
+        <v>21887.39</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>860.02</v>
+        <v>22025.67</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>960.74</v>
+        <v>25910.01</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>1218.14</v>
+        <v>23883.76</v>
       </c>
       <c r="U61" s="34" t="n">
-        <v>4006.04</v>
+        <v>93706.83</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>846.0599999999999</v>
+        <v>25585.14</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>821.52</v>
+        <v>28076.88</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>895.45</v>
+        <v>31994.23</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>724.97</v>
+        <v>26062.67</v>
       </c>
       <c r="Z61" s="34" t="n">
-        <v>3288</v>
+        <v>111718.92</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>644.12</v>
+        <v>25332.05</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>655.04</v>
+        <v>28256.8</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -16368,78 +16256,78 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>2234.36</v>
+        <v>3627.65</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="18" t="n">
-        <v>2491.96</v>
+        <v>12021.04</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>3085.01</v>
+        <v>9857.65</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>3734.54</v>
+        <v>6451.49</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>5407.79</v>
+        <v>5609.28</v>
       </c>
       <c r="K62" s="34" t="n">
-        <v>14719.3</v>
+        <v>33939.46</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>6001.9</v>
+        <v>15751.4</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>5991.99</v>
+        <v>18262.48</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>6040.18</v>
+        <v>18935.77</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>6209.19</v>
+        <v>13632.43</v>
       </c>
       <c r="P62" s="34" t="n">
-        <v>24243.26</v>
+        <v>66582.08</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>6493.93</v>
+        <v>13642.38</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>6189.24</v>
+        <v>8672.82</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>6274.54</v>
+        <v>5765.46</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>6593.13</v>
+        <v>4967.55</v>
       </c>
       <c r="U62" s="34" t="n">
-        <v>25550.84</v>
+        <v>33048.21</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>5857.41</v>
+        <v>7062.19</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>5605.04</v>
+        <v>4038.54</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>6009.09</v>
+        <v>-39.37</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>5003.02</v>
+        <v>-563.96</v>
       </c>
       <c r="Z62" s="34" t="n">
-        <v>22474.56</v>
+        <v>10497.4</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>5693.75</v>
+        <v>13239.25</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>6151.99</v>
+        <v>17990.21</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -16461,78 +16349,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>종속기업,공동지배기업및관계기업관련손익</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>-658.85</v>
+        <v>583.74</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="18" t="n">
-        <v>664.17</v>
+        <v>593.9400000000001</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>1060.77</v>
+        <v>478.79</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>-220.18</v>
+        <v>620.9400000000001</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>-1019.43</v>
+        <v>963.04</v>
       </c>
       <c r="K63" s="34" t="n">
-        <v>485.33</v>
+        <v>2656.71</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>-564.39</v>
+        <v>852.84</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>-191.99</v>
+        <v>828.47</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>-989.23</v>
+        <v>811.14</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>617.24</v>
+        <v>644.24</v>
       </c>
       <c r="P63" s="34" t="n">
-        <v>-1128.37</v>
+        <v>3136.69</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>187.59</v>
+        <v>967.14</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>627.13</v>
+        <v>860.02</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>173.46</v>
+        <v>960.74</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>749.88</v>
+        <v>1218.14</v>
       </c>
       <c r="U63" s="34" t="n">
-        <v>1738.06</v>
+        <v>4006.04</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>-76.47</v>
+        <v>846.0599999999999</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>182.32</v>
+        <v>821.52</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>-130.94</v>
+        <v>895.45</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>1039.84</v>
+        <v>724.97</v>
       </c>
       <c r="Z63" s="34" t="n">
-        <v>1014.75</v>
+        <v>3288</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>1034.14</v>
+        <v>644.12</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>2204.96</v>
+        <v>655.04</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -16554,78 +16442,78 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>지분법관련손익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-658.85</v>
+        <v>2234.36</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="18" t="n">
-        <v>664.17</v>
+        <v>2491.96</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>1060.77</v>
+        <v>3085.01</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-220.18</v>
+        <v>3734.54</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-1019.43</v>
+        <v>5407.79</v>
       </c>
       <c r="K64" s="34" t="n">
-        <v>485.33</v>
+        <v>14719.3</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-564.39</v>
+        <v>6001.9</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-191.99</v>
+        <v>5991.99</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-989.23</v>
+        <v>6040.18</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>617.24</v>
+        <v>6209.19</v>
       </c>
       <c r="P64" s="34" t="n">
-        <v>-1128.37</v>
+        <v>24243.26</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>187.59</v>
+        <v>6493.93</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>627.13</v>
+        <v>6189.24</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>173.46</v>
+        <v>6274.54</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>749.88</v>
+        <v>6593.13</v>
       </c>
       <c r="U64" s="34" t="n">
-        <v>1738.06</v>
+        <v>25550.84</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>-76.47</v>
+        <v>5857.41</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>182.32</v>
+        <v>5605.04</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>-130.94</v>
+        <v>6009.09</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>1039.84</v>
+        <v>5003.02</v>
       </c>
       <c r="Z64" s="34" t="n">
-        <v>1014.75</v>
+        <v>22474.56</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>1034.14</v>
+        <v>5693.75</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>2204.96</v>
+        <v>6151.99</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -16647,78 +16535,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>종속기업,공동지배기업및관계기업관련손익</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>2847.17</v>
+        <v>-658.85</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="18" t="n">
-        <v>4021.64</v>
+        <v>664.17</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>4351.69</v>
+        <v>1060.77</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>43474.57</v>
+        <v>-220.18</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>-868.59</v>
+        <v>-1019.43</v>
       </c>
       <c r="K65" s="34" t="n">
-        <v>50979.31</v>
+        <v>485.33</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>4108.38</v>
+        <v>-564.39</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>3558.89</v>
+        <v>-191.99</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>6242.47</v>
+        <v>-989.23</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>2279.38</v>
+        <v>617.24</v>
       </c>
       <c r="P65" s="34" t="n">
-        <v>16189.12</v>
+        <v>-1128.37</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>3679.77</v>
+        <v>187.59</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>5128.54</v>
+        <v>627.13</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>4565.72</v>
+        <v>173.46</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>5410.03</v>
+        <v>749.88</v>
       </c>
       <c r="U65" s="34" t="n">
-        <v>18784.06</v>
+        <v>1738.06</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>2899.22</v>
+        <v>-76.47</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>4778.35</v>
+        <v>182.32</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>3874.19</v>
+        <v>-130.94</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>2460.32</v>
+        <v>1039.84</v>
       </c>
       <c r="Z65" s="34" t="n">
-        <v>14012.08</v>
+        <v>1014.75</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>15505.54</v>
+        <v>1034.14</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>3377.59</v>
+        <v>2204.96</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -16740,78 +16628,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>지분법관련손익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>351.52</v>
+        <v>-658.85</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>1409.1</v>
+        <v>664.17</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>4483.01</v>
+        <v>1060.77</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>5008.1</v>
+        <v>-220.18</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>2104.4</v>
+        <v>-1019.43</v>
       </c>
       <c r="K66" s="34" t="n">
-        <v>13004.61</v>
+        <v>485.33</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>3754.11</v>
+        <v>-564.39</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>2659.65</v>
+        <v>-191.99</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>2778.08</v>
+        <v>-989.23</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>5037.27</v>
+        <v>617.24</v>
       </c>
       <c r="P66" s="34" t="n">
-        <v>14229.11</v>
+        <v>-1128.37</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>2312.02</v>
+        <v>187.59</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>2982.9</v>
+        <v>627.13</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>1808.59</v>
+        <v>173.46</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>3870.59</v>
+        <v>749.88</v>
       </c>
       <c r="U66" s="34" t="n">
-        <v>10974.1</v>
+        <v>1738.06</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>1475.36</v>
+        <v>-76.47</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>6434.43</v>
+        <v>182.32</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>2860.15</v>
+        <v>-130.94</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>30970.3</v>
+        <v>1039.84</v>
       </c>
       <c r="Z66" s="34" t="n">
-        <v>41740.24</v>
+        <v>1014.75</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>3648.36</v>
+        <v>1034.14</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>3635.51</v>
+        <v>2204.96</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -16833,78 +16721,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-701.76</v>
+        <v>2847.17</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>3501.11</v>
+        <v>4021.64</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>2466.36</v>
+        <v>4351.69</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>3451.28</v>
+        <v>43474.57</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-2461.66</v>
+        <v>-868.59</v>
       </c>
       <c r="K67" s="34" t="n">
-        <v>6957.09</v>
+        <v>50979.31</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>1851.41</v>
+        <v>4108.38</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>1126.39</v>
+        <v>3558.89</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>1195.67</v>
+        <v>6242.47</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-2587.03</v>
+        <v>2279.38</v>
       </c>
       <c r="P67" s="34" t="n">
-        <v>1586.44</v>
+        <v>16189.12</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>1368.94</v>
+        <v>3679.77</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>878.89</v>
+        <v>5128.54</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>714.4299999999999</v>
+        <v>4565.72</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>1244.92</v>
+        <v>5410.03</v>
       </c>
       <c r="U67" s="34" t="n">
-        <v>4207.18</v>
+        <v>18784.06</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>1048.55</v>
+        <v>2899.22</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>1047.06</v>
+        <v>4778.35</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>1335.56</v>
+        <v>3874.19</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>-1480.2</v>
+        <v>2460.32</v>
       </c>
       <c r="Z67" s="34" t="n">
-        <v>1950.97</v>
+        <v>14012.08</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>3929.29</v>
+        <v>15505.54</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>3472.04</v>
+        <v>3377.59</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -16926,78 +16814,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>4515.59</v>
+        <v>351.52</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>9898.620000000001</v>
+        <v>1409.1</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>5714.52</v>
+        <v>4483.01</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>38132.9</v>
+        <v>5008.1</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>-366.24</v>
+        <v>2104.4</v>
       </c>
       <c r="K68" s="34" t="n">
-        <v>53379.8</v>
+        <v>13004.61</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>8540.82</v>
+        <v>3754.11</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>12679.81</v>
+        <v>2659.65</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>14986.22</v>
+        <v>2778.08</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>8581.23</v>
+        <v>5037.27</v>
       </c>
       <c r="P68" s="34" t="n">
-        <v>44788.08</v>
+        <v>14229.11</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>8302</v>
+        <v>2312.02</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>5237.46</v>
+        <v>2982.9</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>2667.82</v>
+        <v>1808.59</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>636.96</v>
+        <v>3870.59</v>
       </c>
       <c r="U68" s="34" t="n">
-        <v>16844.24</v>
+        <v>10974.1</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>2349.68</v>
+        <v>1475.36</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>-3265.8</v>
+        <v>6434.43</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>-5605.46</v>
+        <v>2860.15</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>-30831.96</v>
+        <v>30970.3</v>
       </c>
       <c r="Z68" s="34" t="n">
-        <v>-37353.54</v>
+        <v>41740.24</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>17151.64</v>
+        <v>3648.36</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>10968.27</v>
+        <v>3635.51</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -17019,78 +16907,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>4742.56</v>
+        <v>-701.76</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>11111.57</v>
+        <v>3501.11</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>6198.55</v>
+        <v>2466.36</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>40573.89</v>
+        <v>3451.28</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>-4191.56</v>
+        <v>-2461.66</v>
       </c>
       <c r="K69" s="34" t="n">
-        <v>53692.45</v>
+        <v>6957.09</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>7640.84</v>
+        <v>1851.41</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>12638.68</v>
+        <v>1126.39</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>7983.02</v>
+        <v>1195.67</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>13606.09</v>
+        <v>-2587.03</v>
       </c>
       <c r="P69" s="34" t="n">
-        <v>41868.63</v>
+        <v>1586.44</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>7911.45</v>
+        <v>1368.94</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>4679.44</v>
+        <v>878.89</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>4086.82</v>
+        <v>714.4299999999999</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>2786.43</v>
+        <v>1244.92</v>
       </c>
       <c r="U69" s="34" t="n">
-        <v>19464.14</v>
+        <v>4207.18</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>2392.14</v>
+        <v>1048.55</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>-7259.2</v>
+        <v>1047.06</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>-2088.62</v>
+        <v>1335.56</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>-26904.79</v>
+        <v>-1480.2</v>
       </c>
       <c r="Z69" s="34" t="n">
-        <v>-33860.47</v>
+        <v>1950.97</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>19040.34</v>
+        <v>3929.29</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>9857.91</v>
+        <v>3472.04</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -17112,78 +17000,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>5338.3</v>
+        <v>4515.59</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>9254.309999999999</v>
+        <v>9898.620000000001</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>5781.86</v>
+        <v>5714.52</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>38562.81</v>
+        <v>38132.9</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>-2685.02</v>
+        <v>-366.24</v>
       </c>
       <c r="K70" s="34" t="n">
-        <v>50913.96</v>
+        <v>53379.8</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>7666.83</v>
+        <v>8540.82</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>11566.18</v>
+        <v>12679.81</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>13957.73</v>
+        <v>14986.22</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>5193.65</v>
+        <v>8581.23</v>
       </c>
       <c r="P70" s="34" t="n">
-        <v>38384.39</v>
+        <v>44788.08</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>6278.52</v>
+        <v>8302</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>2654.16</v>
+        <v>5237.46</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>-696.28</v>
+        <v>2667.82</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>-2717.98</v>
+        <v>636.96</v>
       </c>
       <c r="U70" s="34" t="n">
-        <v>5518.42</v>
+        <v>16844.24</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>299.3</v>
+        <v>2349.68</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>-6130.34</v>
+        <v>-3265.8</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>-7859.74</v>
+        <v>-5605.46</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>-31006.47</v>
+        <v>-30831.96</v>
       </c>
       <c r="Z70" s="34" t="n">
-        <v>-44697.25</v>
+        <v>-37353.54</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>14256.8</v>
+        <v>17151.64</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>7270.04</v>
+        <v>10968.27</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -17205,78 +17093,78 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>-822.71</v>
+        <v>4742.56</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="18" t="n">
-        <v>644.3099999999999</v>
+        <v>11111.57</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>-67.34</v>
+        <v>6198.55</v>
       </c>
       <c r="I71" s="18" t="n">
-        <v>-429.91</v>
+        <v>40573.89</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>2318.78</v>
+        <v>-4191.56</v>
       </c>
       <c r="K71" s="34" t="n">
-        <v>2465.84</v>
+        <v>53692.45</v>
       </c>
       <c r="L71" s="18" t="n">
-        <v>873.99</v>
+        <v>7640.84</v>
       </c>
       <c r="M71" s="18" t="n">
-        <v>1113.63</v>
+        <v>12638.68</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>1028.49</v>
+        <v>7983.02</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>3387.58</v>
+        <v>13606.09</v>
       </c>
       <c r="P71" s="34" t="n">
-        <v>6403.69</v>
+        <v>41868.63</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>2023.48</v>
+        <v>7911.45</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>2583.3</v>
+        <v>4679.44</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>3364.09</v>
+        <v>4086.82</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>3354.94</v>
+        <v>2786.43</v>
       </c>
       <c r="U71" s="34" t="n">
-        <v>11325.81</v>
+        <v>19464.14</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>2050.38</v>
+        <v>2392.14</v>
       </c>
       <c r="W71" s="18" t="n">
-        <v>2864.54</v>
+        <v>-7259.2</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>2254.28</v>
+        <v>-2088.62</v>
       </c>
       <c r="Y71" s="18" t="n">
-        <v>174.51</v>
+        <v>-26904.79</v>
       </c>
       <c r="Z71" s="34" t="n">
-        <v>7343.71</v>
+        <v>-33860.47</v>
       </c>
       <c r="AA71" s="18" t="n">
-        <v>2894.84</v>
+        <v>19040.34</v>
       </c>
       <c r="AB71" s="19" t="n">
-        <v>3698.22</v>
+        <v>9857.91</v>
       </c>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
@@ -17298,78 +17186,78 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-1650.62</v>
+        <v>5338.3</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="18" t="n">
-        <v>-1898.02</v>
+        <v>9254.309999999999</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-2606.22</v>
+        <v>5781.86</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-3113.6</v>
+        <v>38562.81</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-4444.75</v>
+        <v>-2685.02</v>
       </c>
       <c r="K72" s="34" t="n">
-        <v>-12062.59</v>
+        <v>50913.96</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-5149.06</v>
+        <v>7666.83</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-5163.52</v>
+        <v>11566.18</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-5229.04</v>
+        <v>13957.73</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-5564.95</v>
+        <v>5193.65</v>
       </c>
       <c r="P72" s="34" t="n">
-        <v>-21106.57</v>
+        <v>38384.39</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>-5526.79</v>
+        <v>6278.52</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>-5329.22</v>
+        <v>2654.16</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>-5313.8</v>
+        <v>-696.28</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>-5374.99</v>
+        <v>-2717.98</v>
       </c>
       <c r="U72" s="34" t="n">
-        <v>-21544.8</v>
+        <v>5518.42</v>
       </c>
       <c r="V72" s="18" t="n">
-        <v>-5011.35</v>
+        <v>299.3</v>
       </c>
       <c r="W72" s="18" t="n">
-        <v>-4783.52</v>
+        <v>-6130.34</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>-5113.64</v>
+        <v>-7859.74</v>
       </c>
       <c r="Y72" s="18" t="n">
-        <v>-4278.05</v>
+        <v>-31006.47</v>
       </c>
       <c r="Z72" s="34" t="n">
-        <v>-19186.56</v>
+        <v>-44697.25</v>
       </c>
       <c r="AA72" s="18" t="n">
-        <v>-5049.63</v>
+        <v>14256.8</v>
       </c>
       <c r="AB72" s="19" t="n">
-        <v>-5496.95</v>
+        <v>7270.04</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -17391,78 +17279,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>(비지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>2495.65</v>
+        <v>-822.71</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="18" t="n">
-        <v>2612.54</v>
+        <v>644.3099999999999</v>
       </c>
       <c r="H73" s="18" t="n">
-        <v>-131.32</v>
+        <v>-67.34</v>
       </c>
       <c r="I73" s="18" t="n">
-        <v>38466.47</v>
+        <v>-429.91</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>-2972.99</v>
+        <v>2318.78</v>
       </c>
       <c r="K73" s="34" t="n">
-        <v>37974.7</v>
+        <v>2465.84</v>
       </c>
       <c r="L73" s="18" t="n">
-        <v>354.27</v>
+        <v>873.99</v>
       </c>
       <c r="M73" s="18" t="n">
-        <v>899.24</v>
+        <v>1113.63</v>
       </c>
       <c r="N73" s="18" t="n">
-        <v>3464.39</v>
+        <v>1028.49</v>
       </c>
       <c r="O73" s="18" t="n">
-        <v>-2757.89</v>
+        <v>3387.58</v>
       </c>
       <c r="P73" s="34" t="n">
-        <v>1960.01</v>
+        <v>6403.69</v>
       </c>
       <c r="Q73" s="18" t="n">
-        <v>1367.75</v>
+        <v>2023.48</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>2145.64</v>
+        <v>2583.3</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>2757.13</v>
+        <v>3364.09</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>1539.44</v>
+        <v>3354.94</v>
       </c>
       <c r="U73" s="34" t="n">
-        <v>7809.96</v>
+        <v>11325.81</v>
       </c>
       <c r="V73" s="18" t="n">
-        <v>1423.86</v>
+        <v>2050.38</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>-1656.08</v>
+        <v>2864.54</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>1014.04</v>
+        <v>2254.28</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>-28509.98</v>
+        <v>174.51</v>
       </c>
       <c r="Z73" s="34" t="n">
-        <v>-27728.16</v>
+        <v>7343.71</v>
       </c>
       <c r="AA73" s="18" t="n">
-        <v>11857.18</v>
+        <v>2894.84</v>
       </c>
       <c r="AB73" s="19" t="n">
-        <v>-257.92</v>
+        <v>3698.22</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -17484,78 +17372,78 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
-        <v>4515.59</v>
+        <v>-1650.62</v>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="18" t="n">
-        <v>9898.620000000001</v>
+        <v>-1898.02</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>5714.52</v>
+        <v>-2606.22</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>38132.9</v>
+        <v>-3113.6</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>-366.24</v>
+        <v>-4444.75</v>
       </c>
       <c r="K74" s="34" t="n">
-        <v>53379.8</v>
+        <v>-12062.59</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>8540.82</v>
+        <v>-5149.06</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>12679.81</v>
+        <v>-5163.52</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>14986.22</v>
+        <v>-5229.04</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>8513.870000000001</v>
+        <v>-5564.95</v>
       </c>
       <c r="P74" s="34" t="n">
-        <v>44720.72</v>
+        <v>-21106.57</v>
       </c>
       <c r="Q74" s="18" t="n">
-        <v>8302</v>
+        <v>-5526.79</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>5237.46</v>
+        <v>-5329.22</v>
       </c>
       <c r="S74" s="18" t="n">
-        <v>2667.82</v>
+        <v>-5313.8</v>
       </c>
       <c r="T74" s="18" t="n">
-        <v>636.96</v>
+        <v>-5374.99</v>
       </c>
       <c r="U74" s="34" t="n">
-        <v>16844.24</v>
+        <v>-21544.8</v>
       </c>
       <c r="V74" s="18" t="n">
-        <v>2349.68</v>
+        <v>-5011.35</v>
       </c>
       <c r="W74" s="18" t="n">
-        <v>-3265.8</v>
+        <v>-4783.52</v>
       </c>
       <c r="X74" s="18" t="n">
-        <v>-5605.46</v>
+        <v>-5113.64</v>
       </c>
       <c r="Y74" s="18" t="n">
-        <v>-30831.96</v>
+        <v>-4278.05</v>
       </c>
       <c r="Z74" s="34" t="n">
-        <v>-37353.54</v>
+        <v>-19186.56</v>
       </c>
       <c r="AA74" s="18" t="n">
-        <v>17151.64</v>
+        <v>-5049.63</v>
       </c>
       <c r="AB74" s="19" t="n">
-        <v>10968.27</v>
+        <v>-5496.95</v>
       </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -17577,70 +17465,78 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
-        </is>
+          <t>기타영업외손익</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="n">
+        <v>2495.65</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="18" t="n">
-        <v>13399.73</v>
+        <v>2612.54</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>8180.87</v>
+        <v>-131.32</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>41584.18</v>
-      </c>
-      <c r="K75" s="9" t="n"/>
+        <v>38466.47</v>
+      </c>
+      <c r="J75" s="18" t="n">
+        <v>-2972.99</v>
+      </c>
+      <c r="K75" s="34" t="n">
+        <v>37974.7</v>
+      </c>
       <c r="L75" s="18" t="n">
-        <v>10392.22</v>
+        <v>354.27</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>13806.2</v>
+        <v>899.24</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>16181.89</v>
+        <v>3464.39</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>5926.84</v>
+        <v>-2757.89</v>
       </c>
       <c r="P75" s="34" t="n">
-        <v>46307.15</v>
+        <v>1960.01</v>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>9670.93</v>
+        <v>1367.75</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>6116.35</v>
+        <v>2145.64</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>3382.25</v>
+        <v>2757.13</v>
       </c>
       <c r="T75" s="18" t="n">
-        <v>1881.88</v>
+        <v>1539.44</v>
       </c>
       <c r="U75" s="34" t="n">
-        <v>21051.41</v>
+        <v>7809.96</v>
       </c>
       <c r="V75" s="18" t="n">
-        <v>3398.23</v>
+        <v>1423.86</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>-2218.74</v>
+        <v>-1656.08</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>-4269.9</v>
+        <v>1014.04</v>
       </c>
       <c r="Y75" s="18" t="n">
-        <v>-32312.16</v>
+        <v>-28509.98</v>
       </c>
       <c r="Z75" s="34" t="n">
-        <v>-35402.57</v>
+        <v>-27728.16</v>
       </c>
       <c r="AA75" s="18" t="n">
-        <v>21080.93</v>
+        <v>11857.18</v>
       </c>
       <c r="AB75" s="19" t="n">
-        <v>14440.3</v>
+        <v>-257.92</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -17662,21 +17558,79 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>중단사업이익</t>
-        </is>
+          <t>계속사업이익</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="n">
+        <v>4515.59</v>
       </c>
       <c r="F76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
+      <c r="G76" s="18" t="n">
+        <v>9898.620000000001</v>
+      </c>
+      <c r="H76" s="18" t="n">
+        <v>5714.52</v>
+      </c>
+      <c r="I76" s="18" t="n">
+        <v>38132.9</v>
+      </c>
+      <c r="J76" s="18" t="n">
+        <v>-366.24</v>
+      </c>
+      <c r="K76" s="34" t="n">
+        <v>53379.8</v>
+      </c>
+      <c r="L76" s="18" t="n">
+        <v>8540.82</v>
+      </c>
+      <c r="M76" s="18" t="n">
+        <v>12679.81</v>
+      </c>
+      <c r="N76" s="18" t="n">
+        <v>14986.22</v>
+      </c>
       <c r="O76" s="18" t="n">
-        <v>67.36</v>
-      </c>
-      <c r="P76" s="9" t="n"/>
-      <c r="U76" s="9" t="n"/>
+        <v>8513.870000000001</v>
+      </c>
+      <c r="P76" s="34" t="n">
+        <v>44720.72</v>
+      </c>
+      <c r="Q76" s="18" t="n">
+        <v>8302</v>
+      </c>
+      <c r="R76" s="18" t="n">
+        <v>5237.46</v>
+      </c>
+      <c r="S76" s="18" t="n">
+        <v>2667.82</v>
+      </c>
+      <c r="T76" s="18" t="n">
+        <v>636.96</v>
+      </c>
+      <c r="U76" s="34" t="n">
+        <v>16844.24</v>
+      </c>
+      <c r="V76" s="18" t="n">
+        <v>2349.68</v>
+      </c>
+      <c r="W76" s="18" t="n">
+        <v>-3265.8</v>
+      </c>
+      <c r="X76" s="18" t="n">
+        <v>-5605.46</v>
+      </c>
       <c r="Y76" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="9" t="n"/>
-      <c r="AB76" s="5" t="n"/>
+        <v>-30831.96</v>
+      </c>
+      <c r="Z76" s="34" t="n">
+        <v>-37353.54</v>
+      </c>
+      <c r="AA76" s="18" t="n">
+        <v>17151.64</v>
+      </c>
+      <c r="AB76" s="19" t="n">
+        <v>10968.27</v>
+      </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
       <c r="AE76" s="11" t="n"/>
@@ -17697,78 +17651,70 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>-20624.88</v>
+          <t>법인세비용차감전계속사업이익</t>
+        </is>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>-7379.67</v>
+        <v>13399.73</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-33035.8</v>
+        <v>8180.87</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>2049.71</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>11497.41</v>
-      </c>
-      <c r="K77" s="34" t="n">
-        <v>-26868.35</v>
-      </c>
+        <v>41584.18</v>
+      </c>
+      <c r="K77" s="9" t="n"/>
       <c r="L77" s="18" t="n">
-        <v>1383.86</v>
+        <v>10392.22</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>13002.49</v>
+        <v>13806.2</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>13278.22</v>
+        <v>16181.89</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>21717.6</v>
+        <v>5926.84</v>
       </c>
       <c r="P77" s="34" t="n">
-        <v>49382.17</v>
+        <v>46307.15</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>3484.62</v>
+        <v>9670.93</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>-15481.3</v>
+        <v>6116.35</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>6934.24</v>
+        <v>3382.25</v>
       </c>
       <c r="T77" s="18" t="n">
-        <v>18073.4</v>
+        <v>1881.88</v>
       </c>
       <c r="U77" s="34" t="n">
-        <v>13010.96</v>
+        <v>21051.41</v>
       </c>
       <c r="V77" s="18" t="n">
-        <v>9210.51</v>
+        <v>3398.23</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>-15227.96</v>
+        <v>-2218.74</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>30312.97</v>
+        <v>-4269.9</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>-2420.88</v>
+        <v>-32312.16</v>
       </c>
       <c r="Z77" s="34" t="n">
-        <v>21874.64</v>
+        <v>-35402.57</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>-10118.94</v>
+        <v>21080.93</v>
       </c>
       <c r="AB77" s="19" t="n">
-        <v>-17484.33</v>
+        <v>14440.3</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -17790,79 +17736,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>14495.29</v>
+          <t>중단사업이익</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>15479.15</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>16425.79</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>16372.54</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>16722.01</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>64999.49</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>15424.78</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>15827.99</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>16210.36</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
       <c r="O78" s="18" t="n">
-        <v>13396.35</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>60859.48</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>14827.91</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>15431.94</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>15858.73</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>15563.15</v>
-      </c>
-      <c r="U78" s="34" t="n">
-        <v>61681.73</v>
-      </c>
-      <c r="V78" s="18" t="n">
-        <v>16407.89</v>
-      </c>
-      <c r="W78" s="18" t="n">
-        <v>16427.79</v>
-      </c>
-      <c r="X78" s="18" t="n">
-        <v>16277.86</v>
-      </c>
+        <v>67.36</v>
+      </c>
+      <c r="P78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
       <c r="Y78" s="18" t="n">
-        <v>17010.4</v>
-      </c>
-      <c r="Z78" s="34" t="n">
-        <v>66123.94</v>
-      </c>
-      <c r="AA78" s="18" t="n">
-        <v>13364.28</v>
-      </c>
-      <c r="AB78" s="19" t="n">
-        <v>15269.63</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="9" t="n"/>
+      <c r="AB78" s="5" t="n"/>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
       <c r="AE78" s="11" t="n"/>
@@ -17883,78 +17771,78 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>무형자산상각비</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>28.4</v>
+        <v>-20624.88</v>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="18" t="n">
-        <v>28.27</v>
+        <v>-7379.67</v>
       </c>
       <c r="H79" s="18" t="n">
-        <v>28.54</v>
+        <v>-33035.8</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>28.41</v>
+        <v>2049.71</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>15.41</v>
+        <v>11497.41</v>
       </c>
       <c r="K79" s="34" t="n">
-        <v>100.63</v>
+        <v>-26868.35</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>12.49</v>
+        <v>1383.86</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>12.54</v>
+        <v>13002.49</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>12.5</v>
+        <v>13278.22</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>13.02</v>
+        <v>21717.6</v>
       </c>
       <c r="P79" s="34" t="n">
-        <v>50.55</v>
+        <v>49382.17</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>14.09</v>
+        <v>3484.62</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>14.81</v>
+        <v>-15481.3</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>20.19</v>
+        <v>6934.24</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>20.95</v>
+        <v>18073.4</v>
       </c>
       <c r="U79" s="34" t="n">
-        <v>70.04000000000001</v>
+        <v>13010.96</v>
       </c>
       <c r="V79" s="18" t="n">
-        <v>20.95</v>
+        <v>9210.51</v>
       </c>
       <c r="W79" s="18" t="n">
-        <v>20.94</v>
+        <v>-15227.96</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>20.95</v>
+        <v>30312.97</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>35.11</v>
+        <v>-2420.88</v>
       </c>
       <c r="Z79" s="34" t="n">
-        <v>97.95</v>
+        <v>21874.64</v>
       </c>
       <c r="AA79" s="18" t="n">
-        <v>42.29</v>
+        <v>-10118.94</v>
       </c>
       <c r="AB79" s="19" t="n">
-        <v>43.05</v>
+        <v>-17484.33</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -17976,78 +17864,78 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
-        <v>21.5</v>
+        <v>14495.29</v>
       </c>
       <c r="F80" s="9" t="n"/>
       <c r="G80" s="18" t="n">
-        <v>0.18</v>
+        <v>15479.15</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>112.38</v>
+        <v>16425.79</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>129.21</v>
+        <v>16372.54</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>2175.58</v>
+        <v>16722.01</v>
       </c>
       <c r="K80" s="34" t="n">
-        <v>2417.35</v>
+        <v>64999.49</v>
       </c>
       <c r="L80" s="18" t="n">
-        <v>0.16</v>
+        <v>15424.78</v>
       </c>
       <c r="M80" s="18" t="n">
-        <v>540.3</v>
+        <v>15827.99</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>-283.43</v>
+        <v>16210.36</v>
       </c>
       <c r="O80" s="18" t="n">
-        <v>53.16</v>
+        <v>13396.35</v>
       </c>
       <c r="P80" s="34" t="n">
-        <v>310.19</v>
+        <v>60859.48</v>
       </c>
       <c r="Q80" s="18" t="n">
-        <v>0.19</v>
+        <v>14827.91</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>846.92</v>
+        <v>15431.94</v>
       </c>
       <c r="S80" s="18" t="n">
-        <v>-477.12</v>
+        <v>15858.73</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>-370.01</v>
+        <v>15563.15</v>
       </c>
       <c r="U80" s="34" t="n">
-        <v>-0.02</v>
+        <v>61681.73</v>
       </c>
       <c r="V80" s="18" t="n">
-        <v>-397.5</v>
+        <v>16407.89</v>
       </c>
       <c r="W80" s="18" t="n">
-        <v>1545.81</v>
+        <v>16427.79</v>
       </c>
       <c r="X80" s="18" t="n">
-        <v>16.61</v>
+        <v>16277.86</v>
       </c>
       <c r="Y80" s="18" t="n">
-        <v>16.6</v>
+        <v>17010.4</v>
       </c>
       <c r="Z80" s="34" t="n">
-        <v>1181.52</v>
+        <v>66123.94</v>
       </c>
       <c r="AA80" s="18" t="n">
-        <v>20.51</v>
+        <v>13364.28</v>
       </c>
       <c r="AB80" s="19" t="n">
-        <v>1632.47</v>
+        <v>15269.63</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -18069,78 +17957,78 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>무형자산상각비</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>-170.52</v>
+        <v>28.4</v>
       </c>
       <c r="F81" s="9" t="n"/>
       <c r="G81" s="18" t="n">
-        <v>1180.26</v>
+        <v>28.27</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>591.88</v>
+        <v>28.54</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>908.28</v>
+        <v>28.41</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>-1187.94</v>
+        <v>15.41</v>
       </c>
       <c r="K81" s="34" t="n">
-        <v>1492.48</v>
+        <v>100.63</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>988.63</v>
+        <v>12.49</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>1167.17</v>
+        <v>12.54</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>1151.29</v>
+        <v>12.5</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>878</v>
+        <v>13.02</v>
       </c>
       <c r="P81" s="34" t="n">
-        <v>4185.09</v>
+        <v>50.55</v>
       </c>
       <c r="Q81" s="18" t="n">
-        <v>1135.39</v>
+        <v>14.09</v>
       </c>
       <c r="R81" s="18" t="n">
-        <v>1110.14</v>
+        <v>14.81</v>
       </c>
       <c r="S81" s="18" t="n">
-        <v>983.41</v>
+        <v>20.19</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>1681.41</v>
+        <v>20.95</v>
       </c>
       <c r="U81" s="34" t="n">
-        <v>4910.35</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="V81" s="18" t="n">
-        <v>1596.3</v>
+        <v>20.95</v>
       </c>
       <c r="W81" s="18" t="n">
-        <v>889.49</v>
+        <v>20.94</v>
       </c>
       <c r="X81" s="18" t="n">
-        <v>934.15</v>
+        <v>20.95</v>
       </c>
       <c r="Y81" s="18" t="n">
-        <v>811.88</v>
+        <v>35.11</v>
       </c>
       <c r="Z81" s="34" t="n">
-        <v>4231.82</v>
+        <v>97.95</v>
       </c>
       <c r="AA81" s="18" t="n">
-        <v>1241.53</v>
+        <v>42.29</v>
       </c>
       <c r="AB81" s="19" t="n">
-        <v>790.5700000000001</v>
+        <v>43.05</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -18162,78 +18050,78 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>-2706.52</v>
+        <v>21.5</v>
       </c>
       <c r="F82" s="9" t="n"/>
       <c r="G82" s="18" t="n">
-        <v>-2456.93</v>
+        <v>0.18</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>-3125.35</v>
+        <v>112.38</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>-4331.48</v>
+        <v>129.21</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>-5331.08</v>
+        <v>2175.58</v>
       </c>
       <c r="K82" s="34" t="n">
-        <v>-15244.84</v>
+        <v>2417.35</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>-6294.85</v>
+        <v>0.16</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>-5774.76</v>
+        <v>540.3</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>-6636.97</v>
+        <v>-283.43</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>-7087.19</v>
+        <v>53.16</v>
       </c>
       <c r="P82" s="34" t="n">
-        <v>-25793.77</v>
+        <v>310.19</v>
       </c>
       <c r="Q82" s="18" t="n">
-        <v>-6331.7</v>
+        <v>0.19</v>
       </c>
       <c r="R82" s="18" t="n">
-        <v>-5839.16</v>
+        <v>846.92</v>
       </c>
       <c r="S82" s="18" t="n">
-        <v>-7109.59</v>
+        <v>-477.12</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>-7244.36</v>
+        <v>-370.01</v>
       </c>
       <c r="U82" s="34" t="n">
-        <v>-26524.81</v>
+        <v>-0.02</v>
       </c>
       <c r="V82" s="18" t="n">
-        <v>-5955.43</v>
+        <v>-397.5</v>
       </c>
       <c r="W82" s="18" t="n">
-        <v>-5846.5</v>
+        <v>1545.81</v>
       </c>
       <c r="X82" s="18" t="n">
-        <v>-5439.81</v>
+        <v>16.61</v>
       </c>
       <c r="Y82" s="18" t="n">
-        <v>-5679.15</v>
+        <v>16.6</v>
       </c>
       <c r="Z82" s="34" t="n">
-        <v>-22920.89</v>
+        <v>1181.52</v>
       </c>
       <c r="AA82" s="18" t="n">
-        <v>-5267.61</v>
+        <v>20.51</v>
       </c>
       <c r="AB82" s="19" t="n">
-        <v>-5737.47</v>
+        <v>1632.47</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -18255,78 +18143,78 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>-5.08</v>
+        <v>-170.52</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>-1774</v>
+        <v>1180.26</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>-2083.06</v>
+        <v>591.88</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>-2484.41</v>
+        <v>908.28</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>19.62</v>
+        <v>-1187.94</v>
       </c>
       <c r="K83" s="34" t="n">
-        <v>-6321.85</v>
+        <v>1492.48</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>-4170.89</v>
+        <v>988.63</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>-5216.84</v>
+        <v>1167.17</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>-2572.92</v>
+        <v>1151.29</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>-2063.45</v>
+        <v>878</v>
       </c>
       <c r="P83" s="34" t="n">
-        <v>-14024.1</v>
+        <v>4185.09</v>
       </c>
       <c r="Q83" s="18" t="n">
-        <v>617.73</v>
+        <v>1135.39</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>-4097.32</v>
+        <v>1110.14</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>-2359.15</v>
+        <v>983.41</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>-597.52</v>
+        <v>1681.41</v>
       </c>
       <c r="U83" s="34" t="n">
-        <v>-6436.26</v>
+        <v>4910.35</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>-1055.65</v>
+        <v>1596.3</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>43.01</v>
+        <v>889.49</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>-1222.23</v>
+        <v>934.15</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>-160.42</v>
+        <v>811.88</v>
       </c>
       <c r="Z83" s="34" t="n">
-        <v>-2395.29</v>
+        <v>4231.82</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>213.98</v>
+        <v>1241.53</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>-451.13</v>
+        <v>790.5700000000001</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -18348,78 +18236,78 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>4701.92</v>
+        <v>-2706.52</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>482.05</v>
+        <v>-2456.93</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>-12669.27</v>
+        <v>-3125.35</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>-15206.98</v>
+        <v>-4331.48</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>-9643.940000000001</v>
+        <v>-5331.08</v>
       </c>
       <c r="K84" s="34" t="n">
-        <v>-37038.14</v>
+        <v>-15244.84</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>-17981.98</v>
+        <v>-6294.85</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>7722.79</v>
+        <v>-5774.76</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>-6577</v>
+        <v>-6636.97</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>-7936.75</v>
+        <v>-7087.19</v>
       </c>
       <c r="P84" s="34" t="n">
-        <v>-24772.94</v>
+        <v>-25793.77</v>
       </c>
       <c r="Q84" s="18" t="n">
-        <v>-11713.94</v>
+        <v>-6331.7</v>
       </c>
       <c r="R84" s="18" t="n">
-        <v>-28109.91</v>
+        <v>-5839.16</v>
       </c>
       <c r="S84" s="18" t="n">
-        <v>-5774.27</v>
+        <v>-7109.59</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>-16618.16</v>
+        <v>-7244.36</v>
       </c>
       <c r="U84" s="34" t="n">
-        <v>-62216.28</v>
+        <v>-26524.81</v>
       </c>
       <c r="V84" s="18" t="n">
-        <v>6737.52</v>
+        <v>-5955.43</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>836.91</v>
+        <v>-5846.5</v>
       </c>
       <c r="X84" s="18" t="n">
-        <v>-17927.76</v>
+        <v>-5439.81</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>-3644.66</v>
+        <v>-5679.15</v>
       </c>
       <c r="Z84" s="34" t="n">
-        <v>-13997.99</v>
+        <v>-22920.89</v>
       </c>
       <c r="AA84" s="18" t="n">
-        <v>7788.16</v>
+        <v>-5267.61</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>-22416.2</v>
+        <v>-5737.47</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -18441,78 +18329,78 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>12248.7</v>
+        <v>-5.08</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>8071.61</v>
+        <v>-1774</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>140.98</v>
+        <v>-2083.06</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>661.6900000000001</v>
+        <v>-2484.41</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>545.78</v>
+        <v>19.62</v>
       </c>
       <c r="K85" s="34" t="n">
-        <v>9420.059999999999</v>
+        <v>-6321.85</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>486.86</v>
+        <v>-4170.89</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>2879.49</v>
+        <v>-5216.84</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>7986.41</v>
+        <v>-2572.92</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>4169.68</v>
+        <v>-2063.45</v>
       </c>
       <c r="P85" s="34" t="n">
-        <v>15522.44</v>
+        <v>-14024.1</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>6253.88</v>
+        <v>617.73</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>6080.11</v>
+        <v>-4097.32</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>1275.13</v>
+        <v>-2359.15</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>2709.72</v>
+        <v>-597.52</v>
       </c>
       <c r="U85" s="34" t="n">
-        <v>16318.84</v>
+        <v>-6436.26</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>1780.21</v>
+        <v>-1055.65</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>1309.44</v>
+        <v>43.01</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>427.2</v>
+        <v>-1222.23</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>922.0599999999999</v>
+        <v>-160.42</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>4438.91</v>
+        <v>-2395.29</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>1090.43</v>
+        <v>213.98</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>2019.29</v>
+        <v>-451.13</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -18534,66 +18422,79 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>무형자산의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>0</v>
+        <v>4701.92</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>273.64</v>
+        <v>482.05</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>0</v>
+        <v>-12669.27</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>0</v>
+        <v>-15206.98</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>0</v>
+        <v>-9643.940000000001</v>
       </c>
       <c r="K86" s="34" t="n">
-        <v>273.64</v>
+        <v>-37038.14</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>0</v>
+        <v>-17981.98</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>1004.18</v>
+        <v>7722.79</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>22.23</v>
+        <v>-6577</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>43.1</v>
+        <v>-7936.75</v>
       </c>
       <c r="P86" s="34" t="n">
-        <v>1069.51</v>
+        <v>-24772.94</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>170</v>
+        <v>-11713.94</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>0</v>
+        <v>-28109.91</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>0</v>
+        <v>-5774.27</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>0</v>
+        <v>-16618.16</v>
       </c>
       <c r="U86" s="34" t="n">
-        <v>170</v>
+        <v>-62216.28</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>0</v>
+        <v>6737.52</v>
+      </c>
+      <c r="W86" s="18" t="n">
+        <v>836.91</v>
+      </c>
+      <c r="X86" s="18" t="n">
+        <v>-17927.76</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>116.64</v>
-      </c>
-      <c r="Z86" s="9" t="n"/>
-      <c r="AB86" s="5" t="n"/>
+        <v>-3644.66</v>
+      </c>
+      <c r="Z86" s="34" t="n">
+        <v>-13997.99</v>
+      </c>
+      <c r="AA86" s="18" t="n">
+        <v>7788.16</v>
+      </c>
+      <c r="AB86" s="19" t="n">
+        <v>-22416.2</v>
+      </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -18614,78 +18515,78 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>4983.76</v>
+        <v>12248.7</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>3149.21</v>
+        <v>8071.61</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>9066.98</v>
+        <v>140.98</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>3844.09</v>
+        <v>661.6900000000001</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>6721.06</v>
+        <v>545.78</v>
       </c>
       <c r="K87" s="34" t="n">
-        <v>22781.34</v>
+        <v>9420.059999999999</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>16976.63</v>
+        <v>486.86</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>6908.99</v>
+        <v>2879.49</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>12597.33</v>
+        <v>7986.41</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>10726.14</v>
+        <v>4169.68</v>
       </c>
       <c r="P87" s="34" t="n">
-        <v>47209.09</v>
+        <v>15522.44</v>
       </c>
       <c r="Q87" s="18" t="n">
-        <v>21851.08</v>
+        <v>6253.88</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>19693.08</v>
+        <v>6080.11</v>
       </c>
       <c r="S87" s="18" t="n">
-        <v>3350.66</v>
+        <v>1275.13</v>
       </c>
       <c r="T87" s="18" t="n">
-        <v>10459.73</v>
+        <v>2709.72</v>
       </c>
       <c r="U87" s="34" t="n">
-        <v>55354.55</v>
+        <v>16318.84</v>
       </c>
       <c r="V87" s="18" t="n">
-        <v>3917.71</v>
+        <v>1780.21</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>2885.65</v>
+        <v>1309.44</v>
       </c>
       <c r="X87" s="18" t="n">
-        <v>14972.97</v>
+        <v>427.2</v>
       </c>
       <c r="Y87" s="18" t="n">
-        <v>23681.47</v>
+        <v>922.0599999999999</v>
       </c>
       <c r="Z87" s="34" t="n">
-        <v>45457.8</v>
+        <v>4438.91</v>
       </c>
       <c r="AA87" s="18" t="n">
-        <v>9083.35</v>
+        <v>1090.43</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>23346.77</v>
+        <v>2019.29</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -18707,79 +18608,66 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>무형자산의감소</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>4983.76</v>
+        <v>0</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>3149.21</v>
+        <v>273.64</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>9066.98</v>
+        <v>0</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>3844.09</v>
+        <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>7102.18</v>
+        <v>0</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>23162.46</v>
+        <v>273.64</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>16979.82</v>
+        <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>6918.5</v>
+        <v>1004.18</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>12694.92</v>
+        <v>22.23</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>10738.45</v>
+        <v>43.1</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>47331.69</v>
+        <v>1069.51</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>21851.08</v>
+        <v>170</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>20148</v>
+        <v>0</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>3469.03</v>
+        <v>0</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>10459.73</v>
+        <v>0</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>55927.84</v>
+        <v>170</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>4126.38</v>
-      </c>
-      <c r="W88" s="18" t="n">
-        <v>2886.26</v>
-      </c>
-      <c r="X88" s="18" t="n">
-        <v>17014.79</v>
+        <v>0</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>23821.31</v>
-      </c>
-      <c r="Z88" s="34" t="n">
-        <v>47848.74</v>
-      </c>
-      <c r="AA88" s="18" t="n">
-        <v>9086.48</v>
-      </c>
-      <c r="AB88" s="19" t="n">
-        <v>23358.77</v>
-      </c>
+        <v>116.64</v>
+      </c>
+      <c r="Z88" s="9" t="n"/>
+      <c r="AB88" s="5" t="n"/>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -18800,56 +18688,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0</v>
+        <v>4983.76</v>
       </c>
       <c r="F89" s="9" t="n"/>
-      <c r="K89" s="9" t="n"/>
+      <c r="G89" s="18" t="n">
+        <v>3149.21</v>
+      </c>
+      <c r="H89" s="18" t="n">
+        <v>9066.98</v>
+      </c>
+      <c r="I89" s="18" t="n">
+        <v>3844.09</v>
+      </c>
+      <c r="J89" s="18" t="n">
+        <v>6721.06</v>
+      </c>
+      <c r="K89" s="34" t="n">
+        <v>22781.34</v>
+      </c>
       <c r="L89" s="18" t="n">
-        <v>3.19</v>
+        <v>16976.63</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>9.51</v>
+        <v>6908.99</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>97.59</v>
+        <v>12597.33</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>12.31</v>
+        <v>10726.14</v>
       </c>
       <c r="P89" s="34" t="n">
-        <v>122.6</v>
+        <v>47209.09</v>
+      </c>
+      <c r="Q89" s="18" t="n">
+        <v>21851.08</v>
+      </c>
+      <c r="R89" s="18" t="n">
+        <v>19693.08</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>118.37</v>
+        <v>3350.66</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" s="9" t="n"/>
+        <v>10459.73</v>
+      </c>
+      <c r="U89" s="34" t="n">
+        <v>55354.55</v>
+      </c>
       <c r="V89" s="18" t="n">
-        <v>208.67</v>
+        <v>3917.71</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>0.61</v>
+        <v>2885.65</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>2041.82</v>
+        <v>14972.97</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>139.84</v>
+        <v>23681.47</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>2390.94</v>
+        <v>45457.8</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>3.13</v>
+        <v>9083.35</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>12</v>
+        <v>23346.77</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -18871,78 +18781,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>4381</v>
+        <v>4983.76</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>9352.77</v>
+        <v>3149.21</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>46655.07</v>
+        <v>9066.98</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>12779.84</v>
+        <v>3844.09</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>-10136.73</v>
+        <v>7102.18</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>58650.95</v>
+        <v>23162.46</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>23407.2</v>
+        <v>16979.82</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>-7900.73</v>
+        <v>6918.5</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>-18759.99</v>
+        <v>12694.92</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>-9383.82</v>
+        <v>10738.45</v>
       </c>
       <c r="P90" s="34" t="n">
-        <v>-12637.34</v>
+        <v>47331.69</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>13153.77</v>
+        <v>21851.08</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>14907.28</v>
+        <v>20148</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>12428.21</v>
+        <v>3469.03</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>-5890.72</v>
+        <v>10459.73</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>34598.54</v>
+        <v>55927.84</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>17655.32</v>
+        <v>4126.38</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>9232.77</v>
+        <v>2886.26</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>8317.83</v>
+        <v>17014.79</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>-22223.67</v>
+        <v>23821.31</v>
       </c>
       <c r="Z90" s="34" t="n">
-        <v>12982.25</v>
+        <v>47848.74</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>28131.23</v>
+        <v>9086.48</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>57908.53</v>
+        <v>23358.77</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -18964,73 +18874,56 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>124596.77</v>
+        <v>0</v>
       </c>
       <c r="F91" s="9" t="n"/>
-      <c r="G91" s="18" t="n">
-        <v>138614.8</v>
-      </c>
-      <c r="H91" s="18" t="n">
-        <v>227822.67</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>136905.35</v>
-      </c>
-      <c r="J91" s="18" t="n">
-        <v>140795.39</v>
-      </c>
-      <c r="K91" s="34" t="n">
-        <v>644138.21</v>
-      </c>
+      <c r="K91" s="9" t="n"/>
       <c r="L91" s="18" t="n">
-        <v>170139.75</v>
+        <v>3.19</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>240067.1</v>
+        <v>9.51</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>167713.67</v>
+        <v>97.59</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>124789.76</v>
+        <v>12.31</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>702710.28</v>
-      </c>
-      <c r="Q91" s="18" t="n">
-        <v>151771.12</v>
-      </c>
-      <c r="R91" s="18" t="n">
-        <v>213536.21</v>
+        <v>122.6</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>200639.42</v>
+        <v>118.37</v>
+      </c>
+      <c r="T91" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="U91" s="9" t="n"/>
       <c r="V91" s="18" t="n">
-        <v>67623.7</v>
+        <v>208.67</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>110643.17</v>
+        <v>0.61</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>99302.92999999999</v>
+        <v>2041.82</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>109206.44</v>
+        <v>139.84</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>386776.24</v>
+        <v>2390.94</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>81669.59</v>
+        <v>3.13</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>100539.7</v>
+        <v>12</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -19052,59 +18945,78 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>2999.58</v>
+        <v>4381</v>
       </c>
       <c r="F92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>9352.77</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>46655.07</v>
+      </c>
       <c r="I92" s="18" t="n">
-        <v>4540</v>
+        <v>12779.84</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>585</v>
-      </c>
-      <c r="K92" s="9" t="n"/>
+        <v>-10136.73</v>
+      </c>
+      <c r="K92" s="34" t="n">
+        <v>58650.95</v>
+      </c>
       <c r="L92" s="18" t="n">
-        <v>4300</v>
+        <v>23407.2</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>4164.68</v>
+        <v>-7900.73</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>5597.32</v>
+        <v>-18759.99</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>2000</v>
+        <v>-9383.82</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>16062</v>
+        <v>-12637.34</v>
       </c>
       <c r="Q92" s="18" t="n">
-        <v>5000</v>
+        <v>13153.77</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>23572.71</v>
+        <v>14907.28</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>40000</v>
+        <v>12428.21</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>15239.29</v>
+        <v>-5890.72</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>83812</v>
+        <v>34598.54</v>
+      </c>
+      <c r="V92" s="18" t="n">
+        <v>17655.32</v>
+      </c>
+      <c r="W92" s="18" t="n">
+        <v>9232.77</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Z92" s="9" t="n"/>
+        <v>8317.83</v>
+      </c>
+      <c r="Y92" s="18" t="n">
+        <v>-22223.67</v>
+      </c>
+      <c r="Z92" s="34" t="n">
+        <v>12982.25</v>
+      </c>
       <c r="AA92" s="18" t="n">
-        <v>10000</v>
+        <v>28131.23</v>
       </c>
       <c r="AB92" s="19" t="n">
-        <v>14885.52</v>
+        <v>57908.53</v>
       </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
@@ -19126,73 +19038,73 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>120848.17</v>
+        <v>124596.77</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>147210.54</v>
+        <v>138614.8</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>181976.92</v>
+        <v>227822.67</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>155953.53</v>
+        <v>136905.35</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>151366.37</v>
+        <v>140795.39</v>
       </c>
       <c r="K93" s="34" t="n">
-        <v>636507.36</v>
+        <v>644138.21</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>149300.18</v>
+        <v>170139.75</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>223279.24</v>
+        <v>240067.1</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>181959.62</v>
+        <v>167713.67</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>124399.67</v>
+        <v>124789.76</v>
       </c>
       <c r="P93" s="34" t="n">
-        <v>678938.71</v>
+        <v>702710.28</v>
       </c>
       <c r="Q93" s="18" t="n">
-        <v>136080.81</v>
+        <v>151771.12</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>226390.66</v>
+        <v>213536.21</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>216283.86</v>
+        <v>200639.42</v>
       </c>
       <c r="U93" s="9" t="n"/>
       <c r="V93" s="18" t="n">
-        <v>71737.78999999999</v>
+        <v>67623.7</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>105808.59</v>
+        <v>110643.17</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>117050.51</v>
+        <v>99302.92999999999</v>
       </c>
       <c r="Y93" s="18" t="n">
-        <v>86848.09</v>
+        <v>109206.44</v>
       </c>
       <c r="Z93" s="34" t="n">
-        <v>381444.98</v>
+        <v>386776.24</v>
       </c>
       <c r="AA93" s="18" t="n">
-        <v>74095.72</v>
+        <v>81669.59</v>
       </c>
       <c r="AB93" s="19" t="n">
-        <v>101218.34</v>
+        <v>100539.7</v>
       </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
@@ -19214,69 +19126,60 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>장기차입금의증가</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>1799.99</v>
+        <v>2999.58</v>
       </c>
       <c r="F94" s="9" t="n"/>
-      <c r="G94" s="18" t="n">
-        <v>1383.33</v>
-      </c>
-      <c r="H94" s="18" t="n">
-        <v>1383.33</v>
-      </c>
       <c r="I94" s="18" t="n">
-        <v>1383.33</v>
+        <v>4540</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>7083.33</v>
-      </c>
-      <c r="K94" s="34" t="n">
-        <v>11233.32</v>
-      </c>
+        <v>585</v>
+      </c>
+      <c r="K94" s="9" t="n"/>
       <c r="L94" s="18" t="n">
-        <v>1083.33</v>
+        <v>4300</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>23202.48</v>
+        <v>4164.68</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>500</v>
+        <v>5597.32</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>11083.33</v>
+        <v>2000</v>
       </c>
       <c r="P94" s="34" t="n">
-        <v>35869.14</v>
+        <v>16062</v>
       </c>
       <c r="Q94" s="18" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="R94" s="18" t="n">
-        <v>11837</v>
+        <v>23572.71</v>
       </c>
       <c r="S94" s="18" t="n">
-        <v>1640</v>
+        <v>40000</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>481.03</v>
+        <v>15239.29</v>
       </c>
       <c r="U94" s="34" t="n">
-        <v>14458.03</v>
-      </c>
-      <c r="V94" s="18" t="n">
-        <v>1597.72</v>
-      </c>
-      <c r="W94" s="18" t="n">
-        <v>23687.01</v>
+        <v>83812</v>
       </c>
       <c r="X94" s="18" t="n">
-        <v>31647.72</v>
+        <v>24000</v>
       </c>
       <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+      <c r="AA94" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>14885.52</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -19297,78 +19200,73 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>단기차입금의감소</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
-        <v>694.28</v>
+        <v>120848.17</v>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="G95" s="18" t="n">
-        <v>627.9299999999999</v>
+        <v>147210.54</v>
       </c>
       <c r="H95" s="18" t="n">
-        <v>678.22</v>
+        <v>181976.92</v>
       </c>
       <c r="I95" s="18" t="n">
-        <v>655.11</v>
+        <v>155953.53</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>628.4</v>
+        <v>151366.37</v>
       </c>
       <c r="K95" s="34" t="n">
-        <v>2589.66</v>
+        <v>636507.36</v>
       </c>
       <c r="L95" s="18" t="n">
-        <v>649.04</v>
+        <v>149300.18</v>
       </c>
       <c r="M95" s="18" t="n">
-        <v>632.77</v>
+        <v>223279.24</v>
       </c>
       <c r="N95" s="18" t="n">
-        <v>744.84</v>
+        <v>181959.62</v>
       </c>
       <c r="O95" s="18" t="n">
-        <v>690.5700000000001</v>
+        <v>124399.67</v>
       </c>
       <c r="P95" s="34" t="n">
-        <v>2717.22</v>
+        <v>678938.71</v>
       </c>
       <c r="Q95" s="18" t="n">
-        <v>762.1</v>
+        <v>136080.81</v>
       </c>
       <c r="R95" s="18" t="n">
-        <v>764.84</v>
+        <v>226390.66</v>
       </c>
       <c r="S95" s="18" t="n">
-        <v>781.38</v>
-      </c>
-      <c r="T95" s="18" t="n">
-        <v>815.3</v>
-      </c>
-      <c r="U95" s="34" t="n">
-        <v>3123.62</v>
-      </c>
+        <v>216283.86</v>
+      </c>
+      <c r="U95" s="9" t="n"/>
       <c r="V95" s="18" t="n">
-        <v>868.63</v>
+        <v>71737.78999999999</v>
       </c>
       <c r="W95" s="18" t="n">
-        <v>805.65</v>
+        <v>105808.59</v>
       </c>
       <c r="X95" s="18" t="n">
-        <v>924.59</v>
+        <v>117050.51</v>
       </c>
       <c r="Y95" s="18" t="n">
-        <v>884.26</v>
+        <v>86848.09</v>
       </c>
       <c r="Z95" s="34" t="n">
-        <v>3483.13</v>
+        <v>381444.98</v>
       </c>
       <c r="AA95" s="18" t="n">
-        <v>864.97</v>
+        <v>74095.72</v>
       </c>
       <c r="AB95" s="19" t="n">
-        <v>638.41</v>
+        <v>101218.34</v>
       </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
@@ -19390,33 +19288,66 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>유동성장기부채의감소</t>
         </is>
       </c>
       <c r="E96" s="18" t="n">
-        <v>0</v>
+        <v>1799.99</v>
       </c>
       <c r="F96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>1383.33</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>1383.33</v>
+      </c>
       <c r="I96" s="18" t="n">
-        <v>0</v>
+        <v>1383.33</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="9" t="n"/>
+        <v>7083.33</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>11233.32</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>1083.33</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>23202.48</v>
+      </c>
+      <c r="N96" s="18" t="n">
+        <v>500</v>
+      </c>
       <c r="O96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P96" s="9" t="n"/>
+        <v>11083.33</v>
+      </c>
+      <c r="P96" s="34" t="n">
+        <v>35869.14</v>
+      </c>
+      <c r="Q96" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>11837</v>
+      </c>
+      <c r="S96" s="18" t="n">
+        <v>1640</v>
+      </c>
       <c r="T96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" s="9" t="n"/>
+        <v>481.03</v>
+      </c>
+      <c r="U96" s="34" t="n">
+        <v>14458.03</v>
+      </c>
+      <c r="V96" s="18" t="n">
+        <v>1597.72</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>23687.01</v>
+      </c>
       <c r="X96" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="18" t="n">
-        <v>0</v>
+        <v>31647.72</v>
       </c>
       <c r="Z96" s="9" t="n"/>
       <c r="AB96" s="5" t="n"/>
@@ -19440,58 +19371,79 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>사채의증가</t>
-        </is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>694.28</v>
       </c>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="18" t="n">
-        <v>19959.78</v>
+        <v>627.9299999999999</v>
       </c>
       <c r="H97" s="18" t="n">
-        <v>0</v>
+        <v>678.22</v>
       </c>
       <c r="I97" s="18" t="n">
-        <v>30000</v>
+        <v>655.11</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>9979.879999999999</v>
+        <v>628.4</v>
       </c>
       <c r="K97" s="34" t="n">
-        <v>59939.66</v>
+        <v>2589.66</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>0</v>
+        <v>649.04</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>0</v>
+        <v>632.77</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P97" s="9" t="n"/>
+        <v>744.84</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>690.5700000000001</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>2717.22</v>
+      </c>
+      <c r="Q97" s="18" t="n">
+        <v>762.1</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>764.84</v>
+      </c>
       <c r="S97" s="18" t="n">
-        <v>0</v>
+        <v>781.38</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" s="9" t="n"/>
+        <v>815.3</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>3123.62</v>
+      </c>
       <c r="V97" s="18" t="n">
-        <v>19959.78</v>
+        <v>868.63</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>0</v>
+        <v>805.65</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>30000</v>
+        <v>924.59</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>0</v>
+        <v>884.26</v>
       </c>
       <c r="Z97" s="34" t="n">
-        <v>49959.78</v>
-      </c>
-      <c r="AB97" s="5" t="n"/>
+        <v>3483.13</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>864.97</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>638.41</v>
+      </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
       <c r="AE97" s="11" t="n"/>
@@ -19512,57 +19464,36 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
-        </is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="9" t="n"/>
       <c r="I98" s="18" t="n">
-        <v>-377.44</v>
+        <v>0</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="K98" s="9" t="n"/>
-      <c r="N98" s="18" t="n">
-        <v>-12058.78</v>
-      </c>
       <c r="O98" s="18" t="n">
-        <v>6240.14</v>
+        <v>0</v>
       </c>
       <c r="P98" s="9" t="n"/>
-      <c r="Q98" s="18" t="n">
-        <v>4924.45</v>
-      </c>
-      <c r="R98" s="18" t="n">
-        <v>-28683.93</v>
-      </c>
-      <c r="S98" s="18" t="n">
-        <v>13588.18</v>
-      </c>
       <c r="T98" s="18" t="n">
-        <v>-4435.49</v>
-      </c>
-      <c r="U98" s="34" t="n">
-        <v>-14606.79</v>
-      </c>
-      <c r="V98" s="18" t="n">
-        <v>33603.35</v>
-      </c>
-      <c r="W98" s="18" t="n">
-        <v>-5158.28</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U98" s="9" t="n"/>
       <c r="X98" s="18" t="n">
-        <v>20703.04</v>
+        <v>0</v>
       </c>
       <c r="Y98" s="18" t="n">
-        <v>-28289.21</v>
-      </c>
-      <c r="Z98" s="34" t="n">
-        <v>20858.9</v>
-      </c>
-      <c r="AA98" s="18" t="n">
-        <v>25800.45</v>
-      </c>
-      <c r="AB98" s="19" t="n">
-        <v>18007.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z98" s="9" t="n"/>
+      <c r="AB98" s="5" t="n"/>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
       <c r="AE98" s="11" t="n"/>
@@ -19583,37 +19514,57 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>사채의증가</t>
         </is>
       </c>
       <c r="F99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>19959.78</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>9979.879999999999</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>59939.66</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="N99" s="18" t="n">
-        <v>147</v>
-      </c>
-      <c r="O99" s="18" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="18" t="n">
-        <v>3000</v>
-      </c>
-      <c r="R99" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="S99" s="18" t="n">
         <v>0</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>200</v>
-      </c>
-      <c r="U99" s="34" t="n">
-        <v>3200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U99" s="9" t="n"/>
       <c r="V99" s="18" t="n">
+        <v>19959.78</v>
+      </c>
+      <c r="W99" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n"/>
+      <c r="X99" s="18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="Y99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="34" t="n">
+        <v>49959.78</v>
+      </c>
       <c r="AB99" s="5" t="n"/>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -19635,53 +19586,56 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="F100" s="9" t="n"/>
+      <c r="I100" s="18" t="n">
+        <v>-377.44</v>
+      </c>
       <c r="K100" s="9" t="n"/>
       <c r="N100" s="18" t="n">
-        <v>-11967.94</v>
+        <v>-12058.78</v>
       </c>
       <c r="O100" s="18" t="n">
-        <v>4345.55</v>
+        <v>6240.14</v>
       </c>
       <c r="P100" s="9" t="n"/>
       <c r="Q100" s="18" t="n">
-        <v>107072.44</v>
+        <v>4924.45</v>
       </c>
       <c r="R100" s="18" t="n">
-        <v>-28114.81</v>
+        <v>-28683.93</v>
       </c>
       <c r="S100" s="18" t="n">
-        <v>12110.41</v>
+        <v>13588.18</v>
       </c>
       <c r="T100" s="18" t="n">
-        <v>-3611.28</v>
+        <v>-4435.49</v>
       </c>
       <c r="U100" s="34" t="n">
-        <v>87456.75999999999</v>
+        <v>-14606.79</v>
       </c>
       <c r="V100" s="18" t="n">
-        <v>121129.8</v>
+        <v>33603.35</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>-6242.12</v>
+        <v>-5158.28</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>21282.24</v>
+        <v>20703.04</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>-28948.6</v>
+        <v>-28289.21</v>
       </c>
       <c r="Z100" s="34" t="n">
-        <v>107221.32</v>
+        <v>20858.9</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>134973.03</v>
+        <v>25800.45</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>17349.67</v>
+        <v>18007.99</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -19703,18 +19657,35 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>사채의감소</t>
+          <t>장기차입금의감소</t>
         </is>
       </c>
       <c r="F101" s="9" t="n"/>
       <c r="K101" s="9" t="n"/>
+      <c r="N101" s="18" t="n">
+        <v>147</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P101" s="9" t="n"/>
+      <c r="Q101" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="T101" s="18" t="n">
+        <v>200</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>3200</v>
+      </c>
+      <c r="V101" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="U101" s="9" t="n"/>
-      <c r="V101" s="18" t="n">
-        <v>20000</v>
       </c>
       <c r="Z101" s="9" t="n"/>
       <c r="AB101" s="5" t="n"/>
@@ -19738,18 +19709,54 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>차입금의감소</t>
+          <t>기말현금및현금성자산</t>
         </is>
       </c>
       <c r="F102" s="9" t="n"/>
       <c r="K102" s="9" t="n"/>
+      <c r="N102" s="18" t="n">
+        <v>-11967.94</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>4345.55</v>
+      </c>
       <c r="P102" s="9" t="n"/>
-      <c r="U102" s="9" t="n"/>
-      <c r="Z102" s="9" t="n"/>
+      <c r="Q102" s="18" t="n">
+        <v>107072.44</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>-28114.81</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>12110.41</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>-3611.28</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>87456.75999999999</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>121129.8</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>-6242.12</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>21282.24</v>
+      </c>
+      <c r="Y102" s="18" t="n">
+        <v>-28948.6</v>
+      </c>
+      <c r="Z102" s="34" t="n">
+        <v>107221.32</v>
+      </c>
       <c r="AA102" s="18" t="n">
-        <v>5738.37</v>
-      </c>
-      <c r="AB102" s="5" t="n"/>
+        <v>134973.03</v>
+      </c>
+      <c r="AB102" s="19" t="n">
+        <v>17349.67</v>
+      </c>
       <c r="AC102" s="10" t="n"/>
       <c r="AD102" s="10" t="n"/>
       <c r="AE102" s="11" t="n"/>
@@ -19763,6 +19770,73 @@
       <c r="AM102" s="10" t="n"/>
       <c r="AN102" s="10" t="n"/>
       <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>사채의감소</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+      <c r="P103" s="9" t="n"/>
+      <c r="T103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="9" t="n"/>
+      <c r="V103" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Z103" s="9" t="n"/>
+      <c r="AB103" s="5" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>차입금의감소</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="P104" s="9" t="n"/>
+      <c r="U104" s="9" t="n"/>
+      <c r="Z104" s="9" t="n"/>
+      <c r="AA104" s="18" t="n">
+        <v>5738.37</v>
+      </c>
+      <c r="AB104" s="5" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20023,7 +20097,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4448,7 +4448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5319,35 +5319,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5438,35 +5438,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5557,35 +5557,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5676,35 +5676,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5795,35 +5795,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5914,35 +5914,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6033,35 +6033,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6152,35 +6152,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6287,7 +6287,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4560</v>
+        <v>4565</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6560,7 +6560,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4617.5</v>
+        <v>4600</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4560</v>
+        <v>4565</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02463660282729904</v>
+        <v>0.02463660282730479</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03995916337487649</v>
+        <v>0.03995916337487803</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39504,7 +39504,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41732,7 +41732,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.92</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4448,7 +4448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5319,35 +5319,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5438,35 +5438,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5557,35 +5557,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5676,35 +5676,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5795,35 +5795,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5914,35 +5914,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6033,35 +6033,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6152,35 +6152,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6287,7 +6287,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4565</v>
+        <v>4600</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6560,7 +6560,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4600</v>
+        <v>4605</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9541,11 +9541,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4565</v>
+        <v>4600</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,670원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,630원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39504,7 +39504,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41732,7 +41732,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.95</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="32">
@@ -41742,7 +41742,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="33">
@@ -41782,7 +41782,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.87</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4448,7 +4448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19437,7 +19437,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -5319,35 +5319,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5438,35 +5438,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5557,35 +5557,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5676,35 +5676,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5795,35 +5795,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5914,35 +5914,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6033,35 +6033,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6152,35 +6152,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6560,7 +6560,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4605</v>
+        <v>4603</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9545,7 +9545,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,630원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,565원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -34115,7 +34115,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39504,7 +39504,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1614,79 +1614,19 @@
 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
       </text>
     </comment>
-    <comment ref="AC40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN40" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 120원 유지</t>
       </text>
     </comment>
-    <comment ref="AI41" authorId="0" shapeId="0">
+    <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 120원 유지</t>
       </text>
     </comment>
-    <comment ref="AN41" authorId="0" shapeId="0">
+    <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 120원 유지</t>
@@ -3452,159 +3392,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="Y34" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI -310억 − (비영업손익 -317억 − 12분기 기준선 -36억) × (1 − 24.0%, 모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)) × 지배 비중 1.00(1 − 비지배 비중(8분기 실측)) = -96억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS -1,094.5원</t>
-      </text>
-    </comment>
-    <comment ref="AA34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AB34" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 -282억 × (1 − 세율 24.0% [모델 세율(분기 유효세율이 0~35% 밖·세전 ≤ 0)]) × 지배 비중 1.0000 [1 − 비지배 비중(8분기 실측)] = -96억 ÷ 유통주식수 · 초과 = 비영업손익 -317억 − 12분기 기준선 -36억 · 보고 EPS -1,094원(EPS 행 불변) · 상수 -214.18·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN34" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
@@ -4432,7 +4282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4448,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4336,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4611,50 +4461,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2025Q4 보고 -1,094→조정 -338원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 세율, 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 4.2배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/014280.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/014280.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 일회성 의심 2025Q4: 비영업손익 -317억(영업이익 -6억의 56배, 12분기 중위 37억·기준선 -36억) → 지배NI -310억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -338.5원(보고 -1,094.5원; 초과 비영업손익 -282억 × (1 − 세율 24.0%) × 지배 비중 1.00 = -214억 차감 — 추정, 조정EPS 행)</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 조선사 연결 없음(suppliers.json)): 전년동기 × (1+g) 추세 / 일회성 의심 2025Q4: 비영업손익 -317억(영업이익 -6억의 56배, 12분기 중위 37억·기준선 -36억) → 지배NI -310억·보고 EPS·FY2025 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -338.5원(보고 -1,094.5원; 초과 비영업손익 -282억 × (1 − 세율 24.0%) × 지배 비중 1.00 = -214억 차감 — 추정, 조정EPS 행)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 7.1, "op_wape_pct": 99.1, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 1894.0, "rev_act": 2052.74, "op_pred": 77.15, "op_act": -0.39}, {"q": "2025Q4", "rev_pred": 2042.29, "rev_act": 1871.9, "op_pred": 83.19, "op_act": -5.64}, {"q": "2026Q1", "rev_pred": 1934.7, "rev_act": 1966.68, "op_pred": 78.8, "op_act": 132.39}, {"q": "2026Q2", "rev_pred": 2071.1, "rev_act": 2290.92, "op_pred": 84.36, "op_act": 179.9}]}</t>
         </is>
@@ -4671,7 +4528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO59"/>
+  <dimension ref="A1:AO58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6858,11 +6715,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -6870,19 +6727,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -6890,19 +6747,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$52</f>
+        <f>$D$51</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -7488,11 +7345,11 @@
         <v/>
       </c>
       <c r="AC26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AD26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AE26" s="25">
@@ -7500,19 +7357,19 @@
         <v/>
       </c>
       <c r="AF26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AG26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AH26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AI26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AJ26" s="25">
@@ -7520,19 +7377,19 @@
         <v/>
       </c>
       <c r="AK26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AL26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AM26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AN26" s="26">
-        <f>$D$51</f>
+        <f>$D$50</f>
         <v/>
       </c>
       <c r="AO26" s="25">
@@ -7653,11 +7510,11 @@
         <v/>
       </c>
       <c r="AC27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AD27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AE27" s="25">
@@ -7665,19 +7522,19 @@
         <v/>
       </c>
       <c r="AF27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AG27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AH27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AI27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AJ27" s="25">
@@ -7685,19 +7542,19 @@
         <v/>
       </c>
       <c r="AK27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AL27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AM27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AN27" s="26">
-        <f>$D$53</f>
+        <f>$D$52</f>
         <v/>
       </c>
       <c r="AO27" s="25">
@@ -9220,264 +9077,176 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="22" t="n"/>
-      <c r="G40" s="21" t="n"/>
-      <c r="H40" s="21" t="n"/>
-      <c r="I40" s="21" t="n"/>
-      <c r="J40" s="21">
-        <f>IFERROR(subQ!J34/subQ!E34-1,"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="22" t="n"/>
-      <c r="L40" s="21">
-        <f>IFERROR(subQ!L34/subQ!G34-1,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="21">
-        <f>IFERROR(subQ!M34/subQ!H34-1,"")</f>
-        <v/>
-      </c>
-      <c r="N40" s="21">
-        <f>IFERROR(subQ!N34/subQ!I34-1,"")</f>
-        <v/>
-      </c>
-      <c r="O40" s="21">
-        <f>IFERROR(subQ!O34/subQ!J34-1,"")</f>
-        <v/>
-      </c>
-      <c r="P40" s="22" t="n"/>
-      <c r="Q40" s="21">
-        <f>IFERROR(subQ!Q34/subQ!L34-1,"")</f>
-        <v/>
-      </c>
-      <c r="R40" s="21">
-        <f>IFERROR(subQ!R34/subQ!M34-1,"")</f>
-        <v/>
-      </c>
-      <c r="S40" s="21">
-        <f>IFERROR(subQ!S34/subQ!N34-1,"")</f>
-        <v/>
-      </c>
-      <c r="T40" s="21">
-        <f>IFERROR(subQ!T34/subQ!O34-1,"")</f>
-        <v/>
-      </c>
-      <c r="U40" s="22" t="n"/>
-      <c r="V40" s="21">
-        <f>IFERROR(subQ!V34/subQ!Q34-1,"")</f>
-        <v/>
-      </c>
-      <c r="W40" s="21">
-        <f>IFERROR(subQ!W34/subQ!R34-1,"")</f>
-        <v/>
-      </c>
-      <c r="X40" s="21">
-        <f>IFERROR(subQ!X34/subQ!S34-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y40" s="21">
-        <f>IFERROR(subQ!Y34/subQ!T34-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z40" s="22" t="n"/>
-      <c r="AA40" s="21">
-        <f>IFERROR(subQ!AA34/subQ!V34-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB40" s="23">
-        <f>IFERROR(subQ!AB34/subQ!W34-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC40" s="24" t="n">
-        <v>-1.144273504</v>
-      </c>
-      <c r="AD40" s="24" t="n">
-        <v>-1.084490399</v>
-      </c>
-      <c r="AE40" s="25" t="n"/>
-      <c r="AF40" s="24" t="n">
-        <v>-0.9308563479999999</v>
-      </c>
-      <c r="AG40" s="24" t="n">
-        <v>-0.775136399</v>
-      </c>
-      <c r="AH40" s="24" t="n">
-        <v>-0.052132701</v>
-      </c>
-      <c r="AI40" s="24" t="n">
-        <v>-0.08041958</v>
-      </c>
-      <c r="AJ40" s="25" t="n"/>
-      <c r="AK40" s="24" t="n">
-        <v>-0.063218391</v>
-      </c>
-      <c r="AL40" s="24" t="n">
-        <v>-0.03812825</v>
-      </c>
-      <c r="AM40" s="24" t="n">
-        <v>-0.0625</v>
-      </c>
-      <c r="AN40" s="24" t="n">
-        <v>-0.095057034</v>
-      </c>
-      <c r="AO40" s="25" t="n"/>
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E40" s="27">
+        <f>subQ!E36</f>
+        <v/>
+      </c>
+      <c r="F40" s="28">
+        <f>subQ!F36</f>
+        <v/>
+      </c>
+      <c r="G40" s="27">
+        <f>subQ!G36</f>
+        <v/>
+      </c>
+      <c r="H40" s="27">
+        <f>subQ!H36</f>
+        <v/>
+      </c>
+      <c r="I40" s="27">
+        <f>subQ!I36</f>
+        <v/>
+      </c>
+      <c r="J40" s="27">
+        <f>subQ!J36</f>
+        <v/>
+      </c>
+      <c r="K40" s="28">
+        <f>subQ!K36</f>
+        <v/>
+      </c>
+      <c r="L40" s="27">
+        <f>subQ!L36</f>
+        <v/>
+      </c>
+      <c r="M40" s="27">
+        <f>subQ!M36</f>
+        <v/>
+      </c>
+      <c r="N40" s="27">
+        <f>subQ!N36</f>
+        <v/>
+      </c>
+      <c r="O40" s="27">
+        <f>subQ!O36</f>
+        <v/>
+      </c>
+      <c r="P40" s="28">
+        <f>subQ!P36</f>
+        <v/>
+      </c>
+      <c r="Q40" s="27">
+        <f>subQ!Q36</f>
+        <v/>
+      </c>
+      <c r="R40" s="27">
+        <f>subQ!R36</f>
+        <v/>
+      </c>
+      <c r="S40" s="27">
+        <f>subQ!S36</f>
+        <v/>
+      </c>
+      <c r="T40" s="27">
+        <f>subQ!T36</f>
+        <v/>
+      </c>
+      <c r="U40" s="28">
+        <f>subQ!U36</f>
+        <v/>
+      </c>
+      <c r="V40" s="27">
+        <f>subQ!V36</f>
+        <v/>
+      </c>
+      <c r="W40" s="27">
+        <f>subQ!W36</f>
+        <v/>
+      </c>
+      <c r="X40" s="27">
+        <f>subQ!X36</f>
+        <v/>
+      </c>
+      <c r="Y40" s="27">
+        <f>subQ!Y36</f>
+        <v/>
+      </c>
+      <c r="Z40" s="28">
+        <f>subQ!Z36</f>
+        <v/>
+      </c>
+      <c r="AA40" s="27">
+        <f>subQ!AA36</f>
+        <v/>
+      </c>
+      <c r="AB40" s="29">
+        <f>subQ!AB36</f>
+        <v/>
+      </c>
+      <c r="AC40" s="32" t="n"/>
+      <c r="AD40" s="30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE40" s="31">
+        <f>subQ!AE36</f>
+        <v/>
+      </c>
+      <c r="AF40" s="32" t="n"/>
+      <c r="AG40" s="32" t="n"/>
+      <c r="AH40" s="32" t="n"/>
+      <c r="AI40" s="30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ40" s="31">
+        <f>subQ!AJ36</f>
+        <v/>
+      </c>
+      <c r="AK40" s="32" t="n"/>
+      <c r="AL40" s="32" t="n"/>
+      <c r="AM40" s="32" t="n"/>
+      <c r="AN40" s="30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO40" s="31">
+        <f>subQ!AO36</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E41" s="27">
-        <f>subQ!E36</f>
-        <v/>
-      </c>
-      <c r="F41" s="28">
-        <f>subQ!F36</f>
-        <v/>
-      </c>
-      <c r="G41" s="27">
-        <f>subQ!G36</f>
-        <v/>
-      </c>
-      <c r="H41" s="27">
-        <f>subQ!H36</f>
-        <v/>
-      </c>
-      <c r="I41" s="27">
-        <f>subQ!I36</f>
-        <v/>
-      </c>
-      <c r="J41" s="27">
-        <f>subQ!J36</f>
-        <v/>
-      </c>
-      <c r="K41" s="28">
-        <f>subQ!K36</f>
-        <v/>
-      </c>
-      <c r="L41" s="27">
-        <f>subQ!L36</f>
-        <v/>
-      </c>
-      <c r="M41" s="27">
-        <f>subQ!M36</f>
-        <v/>
-      </c>
-      <c r="N41" s="27">
-        <f>subQ!N36</f>
-        <v/>
-      </c>
-      <c r="O41" s="27">
-        <f>subQ!O36</f>
-        <v/>
-      </c>
-      <c r="P41" s="28">
-        <f>subQ!P36</f>
-        <v/>
-      </c>
-      <c r="Q41" s="27">
-        <f>subQ!Q36</f>
-        <v/>
-      </c>
-      <c r="R41" s="27">
-        <f>subQ!R36</f>
-        <v/>
-      </c>
-      <c r="S41" s="27">
-        <f>subQ!S36</f>
-        <v/>
-      </c>
-      <c r="T41" s="27">
-        <f>subQ!T36</f>
-        <v/>
-      </c>
-      <c r="U41" s="28">
-        <f>subQ!U36</f>
-        <v/>
-      </c>
-      <c r="V41" s="27">
-        <f>subQ!V36</f>
-        <v/>
-      </c>
-      <c r="W41" s="27">
-        <f>subQ!W36</f>
-        <v/>
-      </c>
-      <c r="X41" s="27">
-        <f>subQ!X36</f>
-        <v/>
-      </c>
-      <c r="Y41" s="27">
-        <f>subQ!Y36</f>
-        <v/>
-      </c>
-      <c r="Z41" s="28">
-        <f>subQ!Z36</f>
-        <v/>
-      </c>
-      <c r="AA41" s="27">
-        <f>subQ!AA36</f>
-        <v/>
-      </c>
-      <c r="AB41" s="29">
-        <f>subQ!AB36</f>
-        <v/>
-      </c>
-      <c r="AC41" s="32" t="n"/>
-      <c r="AD41" s="30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AE41" s="31">
-        <f>subQ!AE36</f>
-        <v/>
-      </c>
-      <c r="AF41" s="32" t="n"/>
-      <c r="AG41" s="32" t="n"/>
-      <c r="AH41" s="32" t="n"/>
-      <c r="AI41" s="30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ41" s="31">
-        <f>subQ!AJ36</f>
-        <v/>
-      </c>
-      <c r="AK41" s="32" t="n"/>
-      <c r="AL41" s="32" t="n"/>
-      <c r="AM41" s="32" t="n"/>
-      <c r="AN41" s="30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO41" s="31">
-        <f>subQ!AO36</f>
-        <v/>
-      </c>
+      <c r="F41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="P41" s="9" t="n"/>
+      <c r="U41" s="9" t="n"/>
+      <c r="Z41" s="9" t="n"/>
+      <c r="AB41" s="5" t="n"/>
+      <c r="AC41" s="10" t="n"/>
+      <c r="AD41" s="10" t="n"/>
+      <c r="AE41" s="11" t="n"/>
+      <c r="AF41" s="10" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="11" t="n"/>
+      <c r="AK41" s="10" t="n"/>
+      <c r="AL41" s="10" t="n"/>
+      <c r="AM41" s="10" t="n"/>
+      <c r="AN41" s="10" t="n"/>
+      <c r="AO41" s="11" t="n"/>
     </row>
     <row r="42">
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F42" s="9" t="n"/>
       <c r="K42" s="9" t="n"/>
       <c r="P42" s="9" t="n"/>
@@ -9499,14 +9268,22 @@
       <c r="AO42" s="11" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="n">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,565원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9532,20 +9309,22 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D44" s="34" t="n">
-        <v>4600</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D44" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,565원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9571,22 +9350,20 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D45" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9612,20 +9389,20 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 4.2배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9651,20 +9428,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D47" s="30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 PER 중위 4.2배가 캡 5~30 밖 — 턴어라운드 초기 TTM EPS 왜곡)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -9690,20 +9467,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D48" s="30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -9729,20 +9506,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D49" s="30" t="n">
-        <v>20</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -9768,20 +9545,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D50" s="36" t="n">
+        <v>0.2403254333215423</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.2404) · 최근 12분기 유효세율 28.1% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 5분기(2024Q3~2026Q2)의 법인세/세전 중위 24.0%</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -9807,20 +9584,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2403254333215423</v>
+        <v>0.1340181682325823</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>연결 — 법인세 = MAX(세전,0) × 세율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.2404) · 최근 12분기 유효세율 28.1% 가 5~27% 밖 → 클립 대신 최근 8분기 중 세전 &gt; 0 인 5분기(2024Q3~2026Q2)의 법인세/세전 중위 24.0%</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.134)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -9846,20 +9623,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.1340181682325823</v>
+        <v>1</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.134)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -9885,20 +9662,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>1</v>
+        <v>0.02463660282729904</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0247)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -9924,20 +9701,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02463660282730479</v>
+        <v>0.03995916337487649</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0247)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.04)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -9963,20 +9740,18 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D55" s="36" t="n">
-        <v>0.03995916337487803</v>
-      </c>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.04)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -10002,18 +9777,18 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D56" s="24" t="n"/>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D56" s="30" t="n"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -10039,18 +9814,18 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D57" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -10076,15 +9851,15 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -10109,43 +9884,6 @@
       <c r="AM58" s="10" t="n"/>
       <c r="AN58" s="10" t="n"/>
       <c r="AO58" s="11" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D59" s="16" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="n"/>
-      <c r="K59" s="9" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="U59" s="9" t="n"/>
-      <c r="Z59" s="9" t="n"/>
-      <c r="AB59" s="5" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="11" t="n"/>
-      <c r="AF59" s="10" t="n"/>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="11" t="n"/>
-      <c r="AK59" s="10" t="n"/>
-      <c r="AL59" s="10" t="n"/>
-      <c r="AM59" s="10" t="n"/>
-      <c r="AN59" s="10" t="n"/>
-      <c r="AO59" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10407,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12487,10 +12225,10 @@
         <v>278438.88</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>366503.31</v>
+        <v>325283.63</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>403115.37</v>
+        <v>367192.63</v>
       </c>
       <c r="J24" s="18" t="n">
         <v>390288.61</v>
@@ -12771,11 +12509,26 @@
       <c r="G27" s="18" t="n">
         <v>2295.95</v>
       </c>
+      <c r="H27" s="18" t="n">
+        <v>2262.4</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <v>2228.94</v>
+      </c>
       <c r="J27" s="18" t="n">
         <v>2010.33</v>
       </c>
       <c r="K27" s="37" t="n">
         <v>2010.33</v>
+      </c>
+      <c r="L27" s="18" t="n">
+        <v>2180.86</v>
+      </c>
+      <c r="M27" s="18" t="n">
+        <v>2126.1</v>
+      </c>
+      <c r="N27" s="18" t="n">
+        <v>1939.13</v>
       </c>
       <c r="O27" s="18" t="n">
         <v>2070.85</v>
@@ -12851,11 +12604,26 @@
       <c r="G28" s="18" t="n">
         <v>11175.41</v>
       </c>
+      <c r="H28" s="18" t="n">
+        <v>13485.52</v>
+      </c>
+      <c r="I28" s="18" t="n">
+        <v>13381.93</v>
+      </c>
       <c r="J28" s="18" t="n">
         <v>12888.58</v>
       </c>
       <c r="K28" s="37" t="n">
         <v>12888.58</v>
+      </c>
+      <c r="L28" s="18" t="n">
+        <v>12766.09</v>
+      </c>
+      <c r="M28" s="18" t="n">
+        <v>12346.06</v>
+      </c>
+      <c r="N28" s="18" t="n">
+        <v>11743.01</v>
       </c>
       <c r="O28" s="18" t="n">
         <v>11259.76</v>
@@ -12931,11 +12699,26 @@
       <c r="G29" s="18" t="n">
         <v>2295.95</v>
       </c>
+      <c r="H29" s="18" t="n">
+        <v>2262.4</v>
+      </c>
+      <c r="I29" s="18" t="n">
+        <v>2228.94</v>
+      </c>
       <c r="J29" s="18" t="n">
         <v>2010.33</v>
       </c>
       <c r="K29" s="37" t="n">
         <v>2010.33</v>
+      </c>
+      <c r="L29" s="18" t="n">
+        <v>2180.86</v>
+      </c>
+      <c r="M29" s="18" t="n">
+        <v>2126.1</v>
+      </c>
+      <c r="N29" s="18" t="n">
+        <v>1939.13</v>
       </c>
       <c r="O29" s="18" t="n">
         <v>2070.85</v>
@@ -13464,11 +13247,26 @@
       <c r="G35" s="18" t="n">
         <v>8879.459999999999</v>
       </c>
+      <c r="H35" s="18" t="n">
+        <v>11223.12</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <v>11152.99</v>
+      </c>
       <c r="J35" s="18" t="n">
         <v>10878.25</v>
       </c>
       <c r="K35" s="37" t="n">
         <v>10878.25</v>
+      </c>
+      <c r="L35" s="18" t="n">
+        <v>10585.23</v>
+      </c>
+      <c r="M35" s="18" t="n">
+        <v>10219.96</v>
+      </c>
+      <c r="N35" s="18" t="n">
+        <v>9803.879999999999</v>
       </c>
       <c r="O35" s="18" t="n">
         <v>9188.91</v>
@@ -13544,11 +13342,26 @@
       <c r="G36" s="18" t="n">
         <v>10548.94</v>
       </c>
+      <c r="H36" s="18" t="n">
+        <v>11223.12</v>
+      </c>
+      <c r="I36" s="18" t="n">
+        <v>11152.99</v>
+      </c>
       <c r="J36" s="18" t="n">
         <v>10878.25</v>
       </c>
       <c r="K36" s="37" t="n">
         <v>10878.25</v>
+      </c>
+      <c r="L36" s="18" t="n">
+        <v>10585.23</v>
+      </c>
+      <c r="M36" s="18" t="n">
+        <v>10219.96</v>
+      </c>
+      <c r="N36" s="18" t="n">
+        <v>9803.879999999999</v>
       </c>
       <c r="O36" s="18" t="n">
         <v>9188.91</v>
@@ -14480,25 +14293,25 @@
         <v>405444.86</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>426676.63</v>
+        <v>406676.63</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>496751.85</v>
+        <v>476751.85</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>522603.34</v>
+        <v>462603.34</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>522603.34</v>
+        <v>462603.34</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>546853.9</v>
+        <v>486853.9</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>544785.52</v>
+        <v>484785.52</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>534886.58</v>
+        <v>474886.58</v>
       </c>
       <c r="O46" s="18" t="n">
         <v>525321.33</v>
@@ -14507,13 +14320,13 @@
         <v>525321.33</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>523044.77</v>
+        <v>483044.77</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>562299.45</v>
+        <v>502299.45</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>533858.49</v>
+        <v>513858.49</v>
       </c>
       <c r="T46" s="18" t="n">
         <v>502328.45</v>
@@ -14575,25 +14388,25 @@
         <v>307028.15</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>327130.53</v>
+        <v>307130.53</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>396254.26</v>
+        <v>376254.26</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>432463.05</v>
+        <v>372463.05</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>432463.05</v>
+        <v>372463.05</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>449588.13</v>
+        <v>389588.13</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>435047.65</v>
+        <v>375047.65</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>437116.65</v>
+        <v>377116.65</v>
       </c>
       <c r="O47" s="18" t="n">
         <v>423205.85</v>
@@ -14602,13 +14415,13 @@
         <v>423205.85</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>415972.33</v>
+        <v>375972.33</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>483341.82</v>
+        <v>423341.82</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>442790.45</v>
+        <v>422790.45</v>
       </c>
       <c r="T47" s="18" t="n">
         <v>414871.69</v>
@@ -14763,6 +14576,12 @@
       </c>
       <c r="G49" s="18" t="n">
         <v>21926.43</v>
+      </c>
+      <c r="H49" s="18" t="n">
+        <v>41219.68</v>
+      </c>
+      <c r="I49" s="18" t="n">
+        <v>35922.74</v>
       </c>
       <c r="K49" s="9" t="n"/>
       <c r="O49" s="18" t="n">
@@ -14828,41 +14647,12 @@
       <c r="G50" s="18" t="n">
         <v>50000</v>
       </c>
-      <c r="H50" s="18" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I50" s="18" t="n">
-        <v>20000</v>
-      </c>
-      <c r="J50" s="18" t="n">
-        <v>60000</v>
-      </c>
-      <c r="K50" s="37" t="n">
-        <v>60000</v>
-      </c>
-      <c r="L50" s="18" t="n">
-        <v>60000</v>
-      </c>
-      <c r="M50" s="18" t="n">
-        <v>60000</v>
-      </c>
-      <c r="N50" s="18" t="n">
-        <v>60000</v>
-      </c>
+      <c r="K50" s="9" t="n"/>
       <c r="O50" s="18" t="n">
         <v>60000</v>
       </c>
       <c r="P50" s="37" t="n">
         <v>60000</v>
-      </c>
-      <c r="Q50" s="18" t="n">
-        <v>40000</v>
-      </c>
-      <c r="R50" s="18" t="n">
-        <v>60000</v>
-      </c>
-      <c r="S50" s="18" t="n">
-        <v>20000</v>
       </c>
       <c r="T50" s="18" t="n">
         <v>19967.26</v>
@@ -14930,46 +14720,39 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>단기금융부채(face)</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
-      <c r="H52" s="18" t="n">
-        <v>366503.31</v>
-      </c>
       <c r="I52" s="18" t="n">
-        <v>403115.37</v>
-      </c>
-      <c r="J52" s="18" t="n">
-        <v>390288.61</v>
-      </c>
-      <c r="K52" s="37" t="n">
-        <v>390288.61</v>
-      </c>
+        <v>2077.68</v>
+      </c>
+      <c r="K52" s="9" t="n"/>
       <c r="L52" s="18" t="n">
-        <v>410737.3</v>
+        <v>1769.4</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>406193.92</v>
+        <v>1230.82</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>394319.97</v>
+        <v>218.03</v>
       </c>
       <c r="P52" s="9" t="n"/>
       <c r="Q52" s="18" t="n">
-        <v>421487.33</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>400806.67</v>
+        <v>1092.02</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>416152.66</v>
+        <v>1549.62</v>
       </c>
       <c r="U52" s="9" t="n"/>
+      <c r="X52" s="18" t="n">
+        <v>1358.11</v>
+      </c>
       <c r="Z52" s="9" t="n"/>
-      <c r="AB52" s="19" t="n">
-        <v>392878.52</v>
-      </c>
+      <c r="AB52" s="5" t="n"/>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
       <c r="AE52" s="11" t="n"/>
@@ -14990,39 +14773,40 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>단기금융부채(face)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
-      <c r="I53" s="18" t="n">
-        <v>2077.68</v>
-      </c>
-      <c r="K53" s="9" t="n"/>
+      <c r="J53" s="18" t="n">
+        <v>390288.61</v>
+      </c>
+      <c r="K53" s="37" t="n">
+        <v>390288.61</v>
+      </c>
       <c r="L53" s="18" t="n">
-        <v>1769.4</v>
+        <v>410737.3</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>1230.82</v>
+        <v>406193.92</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>218.03</v>
+        <v>394319.97</v>
       </c>
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="18" t="n">
-        <v>68.93000000000001</v>
+        <v>421487.33</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1092.02</v>
+        <v>400806.67</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>1549.62</v>
+        <v>416152.66</v>
       </c>
       <c r="U53" s="9" t="n"/>
-      <c r="X53" s="18" t="n">
-        <v>1358.11</v>
-      </c>
       <c r="Z53" s="9" t="n"/>
-      <c r="AB53" s="5" t="n"/>
+      <c r="AB53" s="19" t="n">
+        <v>392878.52</v>
+      </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
@@ -19437,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -21610,80 +21394,80 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>비유동부채</t>
+          <t>유동리스부채</t>
         </is>
       </c>
       <c r="E25" s="18" t="n">
-        <v>52668.28</v>
+        <v>988.35</v>
       </c>
       <c r="F25" s="37" t="n">
-        <v>52668.28</v>
+        <v>988.35</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>63079.03</v>
+        <v>1131.63</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>44536.3</v>
+        <v>1141.03</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>75143.5</v>
+        <v>1174.71</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>71627.11</v>
+        <v>1056.23</v>
       </c>
       <c r="K25" s="37" t="n">
-        <v>71627.11</v>
+        <v>1056.23</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>75112.85000000001</v>
+        <v>1182.66</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>74744.61</v>
+        <v>1117.63</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>74470.47</v>
+        <v>1116.6</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>73357.35000000001</v>
+        <v>1071.03</v>
       </c>
       <c r="P25" s="37" t="n">
-        <v>73357.35000000001</v>
+        <v>1071.03</v>
       </c>
       <c r="Q25" s="18" t="n">
-        <v>50693.98</v>
+        <v>1211.56</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>79440.13</v>
+        <v>1149.59</v>
       </c>
       <c r="S25" s="18" t="n">
-        <v>78921.66</v>
+        <v>1017.49</v>
       </c>
       <c r="T25" s="18" t="n">
-        <v>80086.42</v>
+        <v>905.54</v>
       </c>
       <c r="U25" s="37" t="n">
-        <v>80086.42</v>
+        <v>905.54</v>
       </c>
       <c r="V25" s="18" t="n">
-        <v>99313.64</v>
+        <v>934.85</v>
       </c>
       <c r="W25" s="18" t="n">
-        <v>88416.49000000001</v>
+        <v>1216.26</v>
       </c>
       <c r="X25" s="18" t="n">
-        <v>122692.89</v>
+        <v>1020.99</v>
       </c>
       <c r="Y25" s="18" t="n">
-        <v>120262.57</v>
+        <v>798.17</v>
       </c>
       <c r="Z25" s="37" t="n">
-        <v>120262.57</v>
+        <v>798.17</v>
       </c>
       <c r="AA25" s="18" t="n">
-        <v>122082.92</v>
+        <v>887.24</v>
       </c>
       <c r="AB25" s="19" t="n">
-        <v>131905.04</v>
+        <v>1092.91</v>
       </c>
       <c r="AC25" s="10" t="n"/>
       <c r="AD25" s="10" t="n"/>
@@ -21705,80 +21489,80 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>장기차입금</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="E26" s="18" t="n">
-        <v>42842.13</v>
+        <v>6639.93</v>
       </c>
       <c r="F26" s="37" t="n">
-        <v>42842.13</v>
+        <v>6639.93</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>52879.93</v>
+        <v>7421.46</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>32854.42</v>
+        <v>8726.639999999999</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>62827.74</v>
+        <v>8835.65</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>59952.73</v>
+        <v>8560.65</v>
       </c>
       <c r="K26" s="37" t="n">
-        <v>59952.73</v>
+        <v>8560.65</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>63902.86</v>
+        <v>8548.42</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>62960.6</v>
+        <v>8241.09</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>63915.87</v>
+        <v>8252.530000000001</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>62970.37</v>
+        <v>7959</v>
       </c>
       <c r="P26" s="37" t="n">
-        <v>62970.37</v>
+        <v>7959</v>
       </c>
       <c r="Q26" s="18" t="n">
-        <v>39988.45</v>
+        <v>7810.63</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>69951.06</v>
+        <v>6762.82</v>
       </c>
       <c r="S26" s="18" t="n">
-        <v>69964.09</v>
+        <v>6483.86</v>
       </c>
       <c r="T26" s="18" t="n">
-        <v>69967.25999999999</v>
+        <v>6244.93</v>
       </c>
       <c r="U26" s="37" t="n">
-        <v>69967.25999999999</v>
+        <v>6244.93</v>
       </c>
       <c r="V26" s="18" t="n">
-        <v>89930.32000000001</v>
+        <v>6098.61</v>
       </c>
       <c r="W26" s="18" t="n">
-        <v>79936.69</v>
+        <v>6077.98</v>
       </c>
       <c r="X26" s="18" t="n">
-        <v>113943.2</v>
+        <v>5739.46</v>
       </c>
       <c r="Y26" s="18" t="n">
-        <v>113949.77</v>
+        <v>5389.7</v>
       </c>
       <c r="Z26" s="37" t="n">
-        <v>113949.77</v>
+        <v>5389.7</v>
       </c>
       <c r="AA26" s="18" t="n">
-        <v>113956.26</v>
+        <v>5353.17</v>
       </c>
       <c r="AB26" s="19" t="n">
-        <v>122975.88</v>
+        <v>5441.83</v>
       </c>
       <c r="AC26" s="10" t="n"/>
       <c r="AD26" s="10" t="n"/>
@@ -21800,35 +21584,81 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
+          <t>단기금융부채</t>
         </is>
       </c>
       <c r="E27" s="18" t="n">
-        <v>877.63</v>
+        <v>988.35</v>
       </c>
       <c r="F27" s="37" t="n">
-        <v>877.63</v>
+        <v>988.35</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>953.64</v>
+        <v>1131.63</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>901.4299999999999</v>
+        <v>1141.03</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>868.26</v>
-      </c>
-      <c r="K27" s="9" t="n"/>
+        <v>1174.71</v>
+      </c>
+      <c r="J27" s="18" t="n">
+        <v>1056.23</v>
+      </c>
+      <c r="K27" s="37" t="n">
+        <v>1056.23</v>
+      </c>
       <c r="L27" s="18" t="n">
-        <v>948.26</v>
+        <v>1182.66</v>
+      </c>
+      <c r="M27" s="18" t="n">
+        <v>1117.63</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>949.26</v>
-      </c>
-      <c r="P27" s="9" t="n"/>
-      <c r="U27" s="9" t="n"/>
-      <c r="Z27" s="9" t="n"/>
-      <c r="AB27" s="5" t="n"/>
+        <v>1116.6</v>
+      </c>
+      <c r="O27" s="18" t="n">
+        <v>1071.03</v>
+      </c>
+      <c r="P27" s="37" t="n">
+        <v>1071.03</v>
+      </c>
+      <c r="Q27" s="18" t="n">
+        <v>1211.56</v>
+      </c>
+      <c r="R27" s="18" t="n">
+        <v>1149.59</v>
+      </c>
+      <c r="S27" s="18" t="n">
+        <v>1017.49</v>
+      </c>
+      <c r="T27" s="18" t="n">
+        <v>905.54</v>
+      </c>
+      <c r="U27" s="37" t="n">
+        <v>905.54</v>
+      </c>
+      <c r="V27" s="18" t="n">
+        <v>934.85</v>
+      </c>
+      <c r="W27" s="18" t="n">
+        <v>1216.26</v>
+      </c>
+      <c r="X27" s="18" t="n">
+        <v>1020.99</v>
+      </c>
+      <c r="Y27" s="18" t="n">
+        <v>798.17</v>
+      </c>
+      <c r="Z27" s="37" t="n">
+        <v>798.17</v>
+      </c>
+      <c r="AA27" s="18" t="n">
+        <v>887.24</v>
+      </c>
+      <c r="AB27" s="19" t="n">
+        <v>1092.91</v>
+      </c>
       <c r="AC27" s="10" t="n"/>
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="11" t="n"/>
@@ -21849,75 +21679,80 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>비유동부채</t>
         </is>
       </c>
       <c r="E28" s="18" t="n">
-        <v>3037.01</v>
+        <v>52668.28</v>
       </c>
       <c r="F28" s="37" t="n">
-        <v>3037.01</v>
+        <v>52668.28</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>2828.8</v>
+        <v>63079.03</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>3065.13</v>
+        <v>44536.3</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>3654.28</v>
+        <v>75143.5</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>2126.99</v>
+        <v>71627.11</v>
       </c>
       <c r="K28" s="37" t="n">
-        <v>2126.99</v>
+        <v>71627.11</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>2595.5</v>
+        <v>75112.85000000001</v>
       </c>
       <c r="M28" s="18" t="n">
-        <v>2340.99</v>
+        <v>74744.61</v>
       </c>
       <c r="N28" s="18" t="n">
-        <v>2110.44</v>
+        <v>74470.47</v>
       </c>
       <c r="O28" s="18" t="n">
-        <v>1046.56</v>
+        <v>73357.35000000001</v>
       </c>
       <c r="P28" s="37" t="n">
-        <v>1046.56</v>
+        <v>73357.35000000001</v>
       </c>
       <c r="Q28" s="18" t="n">
-        <v>1544.24</v>
+        <v>50693.98</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>1278.97</v>
+        <v>79440.13</v>
       </c>
       <c r="S28" s="18" t="n">
-        <v>1352.07</v>
+        <v>78921.66</v>
       </c>
       <c r="T28" s="18" t="n">
-        <v>2692.49</v>
+        <v>80086.42</v>
       </c>
       <c r="U28" s="37" t="n">
-        <v>2692.49</v>
+        <v>80086.42</v>
       </c>
       <c r="V28" s="18" t="n">
-        <v>2100.8</v>
+        <v>99313.64</v>
       </c>
       <c r="W28" s="18" t="n">
-        <v>1520.69</v>
+        <v>88416.49000000001</v>
       </c>
       <c r="X28" s="18" t="n">
-        <v>1996.33</v>
-      </c>
-      <c r="Z28" s="9" t="n"/>
+        <v>122692.89</v>
+      </c>
+      <c r="Y28" s="18" t="n">
+        <v>120262.57</v>
+      </c>
+      <c r="Z28" s="37" t="n">
+        <v>120262.57</v>
+      </c>
       <c r="AA28" s="18" t="n">
-        <v>1995.07</v>
+        <v>122082.92</v>
       </c>
       <c r="AB28" s="19" t="n">
-        <v>2976.09</v>
+        <v>131905.04</v>
       </c>
       <c r="AC28" s="10" t="n"/>
       <c r="AD28" s="10" t="n"/>
@@ -21939,80 +21774,80 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>장기충당부채</t>
+          <t>장기차입금</t>
         </is>
       </c>
       <c r="E29" s="18" t="n">
-        <v>1137.56</v>
+        <v>42842.13</v>
       </c>
       <c r="F29" s="37" t="n">
-        <v>1137.56</v>
+        <v>42842.13</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>1080.48</v>
+        <v>52879.93</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>1031.15</v>
+        <v>32854.42</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>1000.55</v>
+        <v>62827.74</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>1174.71</v>
+        <v>59952.73</v>
       </c>
       <c r="K29" s="37" t="n">
-        <v>1174.71</v>
+        <v>59952.73</v>
       </c>
       <c r="L29" s="18" t="n">
-        <v>1248.72</v>
+        <v>63902.86</v>
       </c>
       <c r="M29" s="18" t="n">
-        <v>1330.03</v>
+        <v>62960.6</v>
       </c>
       <c r="N29" s="18" t="n">
-        <v>1308.23</v>
+        <v>63915.87</v>
       </c>
       <c r="O29" s="18" t="n">
-        <v>1494.19</v>
+        <v>62970.37</v>
       </c>
       <c r="P29" s="37" t="n">
-        <v>1494.19</v>
+        <v>62970.37</v>
       </c>
       <c r="Q29" s="18" t="n">
-        <v>1578.3</v>
+        <v>39988.45</v>
       </c>
       <c r="R29" s="18" t="n">
-        <v>1635.6</v>
+        <v>69951.06</v>
       </c>
       <c r="S29" s="18" t="n">
-        <v>1655.25</v>
+        <v>69964.09</v>
       </c>
       <c r="T29" s="18" t="n">
-        <v>1562.97</v>
+        <v>69967.25999999999</v>
       </c>
       <c r="U29" s="37" t="n">
-        <v>1562.97</v>
+        <v>69967.25999999999</v>
       </c>
       <c r="V29" s="18" t="n">
-        <v>1570.39</v>
+        <v>89930.32000000001</v>
       </c>
       <c r="W29" s="18" t="n">
-        <v>1585.33</v>
+        <v>79936.69</v>
       </c>
       <c r="X29" s="18" t="n">
-        <v>1547.83</v>
+        <v>113943.2</v>
       </c>
       <c r="Y29" s="18" t="n">
-        <v>1278.33</v>
+        <v>113949.77</v>
       </c>
       <c r="Z29" s="37" t="n">
-        <v>1278.33</v>
+        <v>113949.77</v>
       </c>
       <c r="AA29" s="18" t="n">
-        <v>1222.71</v>
+        <v>113956.26</v>
       </c>
       <c r="AB29" s="19" t="n">
-        <v>1203.41</v>
+        <v>122975.88</v>
       </c>
       <c r="AC29" s="10" t="n"/>
       <c r="AD29" s="10" t="n"/>
@@ -22034,81 +21869,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="E30" s="18" t="n">
-        <v>303788.48</v>
+        <v>877.63</v>
       </c>
       <c r="F30" s="37" t="n">
-        <v>303788.48</v>
+        <v>877.63</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>313558.78</v>
+        <v>953.64</v>
       </c>
       <c r="H30" s="18" t="n">
-        <v>317747.71</v>
+        <v>901.4299999999999</v>
       </c>
       <c r="I30" s="18" t="n">
-        <v>331935.91</v>
-      </c>
-      <c r="J30" s="18" t="n">
-        <v>344163.96</v>
-      </c>
-      <c r="K30" s="37" t="n">
-        <v>344163.96</v>
-      </c>
+        <v>868.26</v>
+      </c>
+      <c r="K30" s="9" t="n"/>
       <c r="L30" s="18" t="n">
-        <v>364020.22</v>
-      </c>
-      <c r="M30" s="18" t="n">
-        <v>355487.65</v>
+        <v>948.26</v>
       </c>
       <c r="N30" s="18" t="n">
-        <v>352593.92</v>
-      </c>
-      <c r="O30" s="18" t="n">
-        <v>343701.96</v>
-      </c>
-      <c r="P30" s="37" t="n">
-        <v>343701.96</v>
-      </c>
-      <c r="Q30" s="18" t="n">
-        <v>339842.18</v>
-      </c>
-      <c r="R30" s="18" t="n">
-        <v>335403.91</v>
-      </c>
-      <c r="S30" s="18" t="n">
-        <v>338841.66</v>
-      </c>
-      <c r="T30" s="18" t="n">
-        <v>321497.21</v>
-      </c>
-      <c r="U30" s="37" t="n">
-        <v>321497.21</v>
-      </c>
-      <c r="V30" s="18" t="n">
-        <v>336482.95</v>
-      </c>
-      <c r="W30" s="18" t="n">
-        <v>353769.17</v>
-      </c>
-      <c r="X30" s="18" t="n">
-        <v>354141.37</v>
-      </c>
-      <c r="Y30" s="18" t="n">
-        <v>345895.89</v>
-      </c>
-      <c r="Z30" s="37" t="n">
-        <v>345895.89</v>
-      </c>
-      <c r="AA30" s="18" t="n">
-        <v>350320.01</v>
-      </c>
-      <c r="AB30" s="19" t="n">
-        <v>370447.2</v>
-      </c>
+        <v>949.26</v>
+      </c>
+      <c r="P30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="Z30" s="9" t="n"/>
+      <c r="AB30" s="5" t="n"/>
       <c r="AC30" s="10" t="n"/>
       <c r="AD30" s="10" t="n"/>
       <c r="AE30" s="11" t="n"/>
@@ -22129,80 +21918,75 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E31" s="18" t="n">
-        <v>93020.37</v>
+        <v>3037.01</v>
       </c>
       <c r="F31" s="37" t="n">
-        <v>93020.37</v>
+        <v>3037.01</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>93020.37</v>
+        <v>2828.8</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>93020.37</v>
+        <v>3065.13</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>93020.37</v>
+        <v>3654.28</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>93020.37</v>
+        <v>2126.99</v>
       </c>
       <c r="K31" s="37" t="n">
-        <v>93020.37</v>
+        <v>2126.99</v>
       </c>
       <c r="L31" s="18" t="n">
-        <v>93020.37</v>
+        <v>2595.5</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>93020.37</v>
+        <v>2340.99</v>
       </c>
       <c r="N31" s="18" t="n">
-        <v>93020.37</v>
+        <v>2110.44</v>
       </c>
       <c r="O31" s="18" t="n">
-        <v>93020.37</v>
+        <v>1046.56</v>
       </c>
       <c r="P31" s="37" t="n">
-        <v>93020.37</v>
+        <v>1046.56</v>
       </c>
       <c r="Q31" s="18" t="n">
-        <v>93020.37</v>
+        <v>1544.24</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>93020.37</v>
+        <v>1278.97</v>
       </c>
       <c r="S31" s="18" t="n">
-        <v>93020.37</v>
+        <v>1352.07</v>
       </c>
       <c r="T31" s="18" t="n">
-        <v>93020.37</v>
+        <v>2692.49</v>
       </c>
       <c r="U31" s="37" t="n">
-        <v>93020.37</v>
+        <v>2692.49</v>
       </c>
       <c r="V31" s="18" t="n">
-        <v>93020.37</v>
+        <v>2100.8</v>
       </c>
       <c r="W31" s="18" t="n">
-        <v>93020.37</v>
+        <v>1520.69</v>
       </c>
       <c r="X31" s="18" t="n">
-        <v>93020.37</v>
-      </c>
-      <c r="Y31" s="18" t="n">
-        <v>93020.37</v>
-      </c>
-      <c r="Z31" s="37" t="n">
-        <v>93020.37</v>
-      </c>
+        <v>1996.33</v>
+      </c>
+      <c r="Z31" s="9" t="n"/>
       <c r="AA31" s="18" t="n">
-        <v>93020.37</v>
+        <v>1995.07</v>
       </c>
       <c r="AB31" s="19" t="n">
-        <v>93020.37</v>
+        <v>2976.09</v>
       </c>
       <c r="AC31" s="10" t="n"/>
       <c r="AD31" s="10" t="n"/>
@@ -22224,80 +22008,80 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>장기충당부채</t>
         </is>
       </c>
       <c r="E32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1137.56</v>
       </c>
       <c r="F32" s="37" t="n">
-        <v>49143.43</v>
+        <v>1137.56</v>
       </c>
       <c r="G32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1080.48</v>
       </c>
       <c r="H32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1031.15</v>
       </c>
       <c r="I32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1000.55</v>
       </c>
       <c r="J32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1174.71</v>
       </c>
       <c r="K32" s="37" t="n">
-        <v>49143.43</v>
+        <v>1174.71</v>
       </c>
       <c r="L32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1248.72</v>
       </c>
       <c r="M32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1330.03</v>
       </c>
       <c r="N32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1308.23</v>
       </c>
       <c r="O32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1494.19</v>
       </c>
       <c r="P32" s="37" t="n">
-        <v>49143.43</v>
+        <v>1494.19</v>
       </c>
       <c r="Q32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1578.3</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1635.6</v>
       </c>
       <c r="S32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1655.25</v>
       </c>
       <c r="T32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1562.97</v>
       </c>
       <c r="U32" s="37" t="n">
-        <v>49143.43</v>
+        <v>1562.97</v>
       </c>
       <c r="V32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1570.39</v>
       </c>
       <c r="W32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1585.33</v>
       </c>
       <c r="X32" s="18" t="n">
-        <v>49143.43</v>
+        <v>1547.83</v>
       </c>
       <c r="Y32" s="18" t="n">
-        <v>59499.36</v>
+        <v>1278.33</v>
       </c>
       <c r="Z32" s="37" t="n">
-        <v>59499.36</v>
+        <v>1278.33</v>
       </c>
       <c r="AA32" s="18" t="n">
-        <v>59499.36</v>
+        <v>1222.71</v>
       </c>
       <c r="AB32" s="19" t="n">
-        <v>59499.36</v>
+        <v>1203.41</v>
       </c>
       <c r="AC32" s="10" t="n"/>
       <c r="AD32" s="10" t="n"/>
@@ -22319,80 +22103,80 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E33" s="18" t="n">
-        <v>246.37</v>
+        <v>5651.58</v>
       </c>
       <c r="F33" s="37" t="n">
-        <v>246.37</v>
+        <v>5651.58</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>795.37</v>
+        <v>6289.83</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>57.9</v>
+        <v>7585.61</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>-94.38</v>
+        <v>7660.94</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>163.38</v>
+        <v>7504.42</v>
       </c>
       <c r="K33" s="37" t="n">
-        <v>163.38</v>
+        <v>7504.42</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>332.33</v>
+        <v>7365.76</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>390.46</v>
+        <v>7123.46</v>
       </c>
       <c r="N33" s="18" t="n">
-        <v>767.29</v>
+        <v>7135.93</v>
       </c>
       <c r="O33" s="18" t="n">
-        <v>846.62</v>
+        <v>6887.97</v>
       </c>
       <c r="P33" s="37" t="n">
-        <v>846.62</v>
+        <v>6887.97</v>
       </c>
       <c r="Q33" s="18" t="n">
-        <v>344.84</v>
+        <v>6599.07</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>132.31</v>
+        <v>5613.23</v>
       </c>
       <c r="S33" s="18" t="n">
-        <v>-31.92</v>
+        <v>5466.37</v>
       </c>
       <c r="T33" s="18" t="n">
-        <v>-526.34</v>
+        <v>5339.39</v>
       </c>
       <c r="U33" s="37" t="n">
-        <v>-526.34</v>
+        <v>5339.39</v>
       </c>
       <c r="V33" s="18" t="n">
-        <v>-471.5</v>
+        <v>5163.76</v>
       </c>
       <c r="W33" s="18" t="n">
-        <v>-164.58</v>
+        <v>4861.72</v>
       </c>
       <c r="X33" s="18" t="n">
-        <v>-180.87</v>
+        <v>4718.47</v>
       </c>
       <c r="Y33" s="18" t="n">
-        <v>243.01</v>
+        <v>4591.53</v>
       </c>
       <c r="Z33" s="37" t="n">
-        <v>243.01</v>
+        <v>4591.53</v>
       </c>
       <c r="AA33" s="18" t="n">
-        <v>-1050.22</v>
+        <v>4465.93</v>
       </c>
       <c r="AB33" s="19" t="n">
-        <v>-3166.14</v>
+        <v>4348.92</v>
       </c>
       <c r="AC33" s="10" t="n"/>
       <c r="AD33" s="10" t="n"/>
@@ -22414,80 +22198,80 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E34" s="18" t="n">
-        <v>202646.16</v>
+        <v>5651.58</v>
       </c>
       <c r="F34" s="37" t="n">
-        <v>202646.16</v>
+        <v>5651.58</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>211346.15</v>
+        <v>6289.83</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>219344.14</v>
+        <v>7585.61</v>
       </c>
       <c r="I34" s="18" t="n">
-        <v>231394.54</v>
+        <v>7660.94</v>
       </c>
       <c r="J34" s="18" t="n">
-        <v>227423.32</v>
+        <v>7504.42</v>
       </c>
       <c r="K34" s="37" t="n">
-        <v>227423.32</v>
+        <v>7504.42</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>229809.92</v>
+        <v>7365.76</v>
       </c>
       <c r="M34" s="18" t="n">
-        <v>238626.62</v>
+        <v>7123.46</v>
       </c>
       <c r="N34" s="18" t="n">
-        <v>248861.3</v>
+        <v>7135.93</v>
       </c>
       <c r="O34" s="18" t="n">
-        <v>244299.66</v>
+        <v>6887.97</v>
       </c>
       <c r="P34" s="37" t="n">
-        <v>244299.66</v>
+        <v>6887.97</v>
       </c>
       <c r="Q34" s="18" t="n">
-        <v>243338.44</v>
+        <v>6599.07</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>245111.29</v>
+        <v>5613.23</v>
       </c>
       <c r="S34" s="18" t="n">
-        <v>236467.14</v>
+        <v>5466.37</v>
       </c>
       <c r="T34" s="18" t="n">
-        <v>234127.14</v>
+        <v>5339.39</v>
       </c>
       <c r="U34" s="37" t="n">
-        <v>234127.14</v>
+        <v>5339.39</v>
       </c>
       <c r="V34" s="18" t="n">
-        <v>229486.02</v>
+        <v>5163.76</v>
       </c>
       <c r="W34" s="18" t="n">
-        <v>218542.51</v>
+        <v>4861.72</v>
       </c>
       <c r="X34" s="18" t="n">
-        <v>211015.11</v>
+        <v>4718.47</v>
       </c>
       <c r="Y34" s="18" t="n">
-        <v>188866.9</v>
+        <v>4591.53</v>
       </c>
       <c r="Z34" s="37" t="n">
-        <v>188866.9</v>
+        <v>4591.53</v>
       </c>
       <c r="AA34" s="18" t="n">
-        <v>198344.38</v>
+        <v>4465.93</v>
       </c>
       <c r="AB34" s="19" t="n">
-        <v>200351.43</v>
+        <v>4348.92</v>
       </c>
       <c r="AC34" s="10" t="n"/>
       <c r="AD34" s="10" t="n"/>
@@ -22509,80 +22293,80 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E35" s="18" t="n">
-        <v>281955.19</v>
+        <v>303788.48</v>
       </c>
       <c r="F35" s="37" t="n">
-        <v>281955.19</v>
+        <v>303788.48</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>291204.18</v>
+        <v>313558.78</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>298464.7</v>
+        <v>317747.71</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>310362.82</v>
+        <v>331935.91</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>306649.36</v>
+        <v>344163.96</v>
       </c>
       <c r="K35" s="37" t="n">
-        <v>306649.36</v>
+        <v>344163.96</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>309204.92</v>
+        <v>364020.22</v>
       </c>
       <c r="M35" s="18" t="n">
-        <v>318079.75</v>
+        <v>355487.65</v>
       </c>
       <c r="N35" s="18" t="n">
-        <v>328691.25</v>
+        <v>352593.92</v>
       </c>
       <c r="O35" s="18" t="n">
-        <v>324208.94</v>
+        <v>343701.96</v>
       </c>
       <c r="P35" s="37" t="n">
-        <v>324208.94</v>
+        <v>343701.96</v>
       </c>
       <c r="Q35" s="18" t="n">
-        <v>322745.94</v>
+        <v>339842.18</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>324306.26</v>
+        <v>335403.91</v>
       </c>
       <c r="S35" s="18" t="n">
-        <v>315497.89</v>
+        <v>338841.66</v>
       </c>
       <c r="T35" s="18" t="n">
-        <v>312663.46</v>
+        <v>321497.21</v>
       </c>
       <c r="U35" s="37" t="n">
-        <v>312663.46</v>
+        <v>321497.21</v>
       </c>
       <c r="V35" s="18" t="n">
-        <v>308077.19</v>
+        <v>336482.95</v>
       </c>
       <c r="W35" s="18" t="n">
-        <v>297440.59</v>
+        <v>353769.17</v>
       </c>
       <c r="X35" s="18" t="n">
-        <v>289896.9</v>
+        <v>354141.37</v>
       </c>
       <c r="Y35" s="18" t="n">
-        <v>278528.5</v>
+        <v>345895.89</v>
       </c>
       <c r="Z35" s="37" t="n">
-        <v>278528.5</v>
+        <v>345895.89</v>
       </c>
       <c r="AA35" s="18" t="n">
-        <v>286712.75</v>
+        <v>350320.01</v>
       </c>
       <c r="AB35" s="19" t="n">
-        <v>286603.88</v>
+        <v>370447.2</v>
       </c>
       <c r="AC35" s="10" t="n"/>
       <c r="AD35" s="10" t="n"/>
@@ -22604,80 +22388,80 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E36" s="18" t="n">
-        <v>585743.67</v>
+        <v>93020.37</v>
       </c>
       <c r="F36" s="37" t="n">
-        <v>585743.67</v>
+        <v>93020.37</v>
       </c>
       <c r="G36" s="18" t="n">
-        <v>604762.97</v>
+        <v>93020.37</v>
       </c>
       <c r="H36" s="18" t="n">
-        <v>616212.41</v>
+        <v>93020.37</v>
       </c>
       <c r="I36" s="18" t="n">
-        <v>642298.72</v>
+        <v>93020.37</v>
       </c>
       <c r="J36" s="18" t="n">
-        <v>650813.3199999999</v>
+        <v>93020.37</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>650813.3199999999</v>
+        <v>93020.37</v>
       </c>
       <c r="L36" s="18" t="n">
-        <v>673225.14</v>
+        <v>93020.37</v>
       </c>
       <c r="M36" s="18" t="n">
-        <v>673567.4</v>
+        <v>93020.37</v>
       </c>
       <c r="N36" s="18" t="n">
-        <v>681285.17</v>
+        <v>93020.37</v>
       </c>
       <c r="O36" s="18" t="n">
-        <v>667910.9</v>
+        <v>93020.37</v>
       </c>
       <c r="P36" s="37" t="n">
-        <v>667910.9</v>
+        <v>93020.37</v>
       </c>
       <c r="Q36" s="18" t="n">
-        <v>662588.12</v>
+        <v>93020.37</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>659710.17</v>
+        <v>93020.37</v>
       </c>
       <c r="S36" s="18" t="n">
-        <v>654339.55</v>
+        <v>93020.37</v>
       </c>
       <c r="T36" s="18" t="n">
-        <v>634160.67</v>
+        <v>93020.37</v>
       </c>
       <c r="U36" s="37" t="n">
-        <v>634160.67</v>
+        <v>93020.37</v>
       </c>
       <c r="V36" s="18" t="n">
-        <v>644560.14</v>
+        <v>93020.37</v>
       </c>
       <c r="W36" s="18" t="n">
-        <v>651209.76</v>
+        <v>93020.37</v>
       </c>
       <c r="X36" s="18" t="n">
-        <v>644038.27</v>
+        <v>93020.37</v>
       </c>
       <c r="Y36" s="18" t="n">
-        <v>624424.39</v>
+        <v>93020.37</v>
       </c>
       <c r="Z36" s="37" t="n">
-        <v>624424.39</v>
+        <v>93020.37</v>
       </c>
       <c r="AA36" s="18" t="n">
-        <v>637032.77</v>
+        <v>93020.37</v>
       </c>
       <c r="AB36" s="19" t="n">
-        <v>657051.08</v>
+        <v>93020.37</v>
       </c>
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
@@ -22699,80 +22483,80 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>281955.19</v>
+        <v>49143.43</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>281955.19</v>
+        <v>49143.43</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>291204.18</v>
+        <v>49143.43</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>298464.7</v>
+        <v>49143.43</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>310362.82</v>
+        <v>49143.43</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>306649.36</v>
+        <v>49143.43</v>
       </c>
       <c r="K37" s="37" t="n">
-        <v>306649.36</v>
+        <v>49143.43</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>309204.92</v>
+        <v>49143.43</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>318079.75</v>
+        <v>49143.43</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>328691.25</v>
+        <v>49143.43</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>324208.94</v>
+        <v>49143.43</v>
       </c>
       <c r="P37" s="37" t="n">
-        <v>324208.94</v>
+        <v>49143.43</v>
       </c>
       <c r="Q37" s="18" t="n">
-        <v>322745.94</v>
+        <v>49143.43</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>324306.26</v>
+        <v>49143.43</v>
       </c>
       <c r="S37" s="18" t="n">
-        <v>315497.89</v>
+        <v>49143.43</v>
       </c>
       <c r="T37" s="18" t="n">
-        <v>312663.46</v>
+        <v>49143.43</v>
       </c>
       <c r="U37" s="37" t="n">
-        <v>312663.46</v>
+        <v>49143.43</v>
       </c>
       <c r="V37" s="18" t="n">
-        <v>308077.19</v>
+        <v>49143.43</v>
       </c>
       <c r="W37" s="18" t="n">
-        <v>297440.59</v>
+        <v>49143.43</v>
       </c>
       <c r="X37" s="18" t="n">
-        <v>289896.9</v>
+        <v>49143.43</v>
       </c>
       <c r="Y37" s="18" t="n">
-        <v>278528.5</v>
+        <v>59499.36</v>
       </c>
       <c r="Z37" s="37" t="n">
-        <v>278528.5</v>
+        <v>59499.36</v>
       </c>
       <c r="AA37" s="18" t="n">
-        <v>286712.75</v>
+        <v>59499.36</v>
       </c>
       <c r="AB37" s="19" t="n">
-        <v>286603.88</v>
+        <v>59499.36</v>
       </c>
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
@@ -22794,80 +22578,80 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>229383.85</v>
+        <v>246.37</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>229383.85</v>
+        <v>246.37</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>236286.83</v>
+        <v>795.37</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>242543.35</v>
+        <v>57.9</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>258409.76</v>
+        <v>-94.38</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>261895.27</v>
+        <v>163.38</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>261895.27</v>
+        <v>163.38</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>283555.55</v>
+        <v>332.33</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>265587.84</v>
+        <v>390.46</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>265501.6</v>
+        <v>767.29</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>260770.73</v>
+        <v>846.62</v>
       </c>
       <c r="P38" s="37" t="n">
-        <v>260770.73</v>
+        <v>846.62</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>264285.82</v>
+        <v>344.84</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>266753.46</v>
+        <v>132.31</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>280337.48</v>
+        <v>-31.92</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>263285.46</v>
+        <v>-526.34</v>
       </c>
       <c r="U38" s="37" t="n">
-        <v>263285.46</v>
+        <v>-526.34</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>273485.84</v>
+        <v>-471.5</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>281194.34</v>
+        <v>-164.58</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>278467.43</v>
+        <v>-180.87</v>
       </c>
       <c r="Y38" s="18" t="n">
-        <v>280548.34</v>
+        <v>243.01</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>280548.34</v>
+        <v>243.01</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>280050.03</v>
+        <v>-1050.22</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>301543.56</v>
+        <v>-3166.14</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -22889,80 +22673,80 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E39" s="18" t="n">
-        <v>173172.52</v>
+        <v>202646.16</v>
       </c>
       <c r="F39" s="37" t="n">
-        <v>173172.52</v>
+        <v>202646.16</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>173218.61</v>
+        <v>211346.15</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>179986.32</v>
+        <v>219344.14</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>201485.61</v>
+        <v>231394.54</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>206412.87</v>
+        <v>227423.32</v>
       </c>
       <c r="K39" s="37" t="n">
-        <v>206412.87</v>
+        <v>227423.32</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>219494.66</v>
+        <v>229809.92</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>199709.65</v>
+        <v>238626.62</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>198184.34</v>
+        <v>248861.3</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>195656.66</v>
+        <v>244299.66</v>
       </c>
       <c r="P39" s="37" t="n">
-        <v>195656.66</v>
+        <v>244299.66</v>
       </c>
       <c r="Q39" s="18" t="n">
-        <v>203333.87</v>
+        <v>243338.44</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>231054.4</v>
+        <v>245111.29</v>
       </c>
       <c r="S39" s="18" t="n">
-        <v>237837.33</v>
+        <v>236467.14</v>
       </c>
       <c r="T39" s="18" t="n">
-        <v>229665.39</v>
+        <v>234127.14</v>
       </c>
       <c r="U39" s="37" t="n">
-        <v>229665.39</v>
+        <v>234127.14</v>
       </c>
       <c r="V39" s="18" t="n">
-        <v>211007.49</v>
+        <v>229486.02</v>
       </c>
       <c r="W39" s="18" t="n">
-        <v>222097.3</v>
+        <v>218542.51</v>
       </c>
       <c r="X39" s="18" t="n">
-        <v>220079.87</v>
+        <v>211015.11</v>
       </c>
       <c r="Y39" s="18" t="n">
-        <v>239612.03</v>
+        <v>188866.9</v>
       </c>
       <c r="Z39" s="37" t="n">
-        <v>239612.03</v>
+        <v>188866.9</v>
       </c>
       <c r="AA39" s="18" t="n">
-        <v>229154.31</v>
+        <v>198344.38</v>
       </c>
       <c r="AB39" s="19" t="n">
-        <v>256040.64</v>
+        <v>200351.43</v>
       </c>
       <c r="AC39" s="10" t="n"/>
       <c r="AD39" s="10" t="n"/>
@@ -22984,80 +22768,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>64324.31</v>
+        <v>281955.19</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>64324.31</v>
+        <v>281955.19</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>71906.63</v>
+        <v>291204.18</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>70193.96000000001</v>
+        <v>298464.7</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>78918.78999999999</v>
+        <v>310362.82</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>77850.74000000001</v>
+        <v>306649.36</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>77850.74000000001</v>
+        <v>306649.36</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>86709.69</v>
+        <v>309204.92</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>88666.45</v>
+        <v>318079.75</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>84861.5</v>
+        <v>328691.25</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>84103.55</v>
+        <v>324208.94</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>84103.55</v>
+        <v>324208.94</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>79457.13</v>
+        <v>322745.94</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>54018.87</v>
+        <v>324306.26</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>61014.96</v>
+        <v>315497.89</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>41553.91</v>
+        <v>312663.46</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>41553.91</v>
+        <v>312663.46</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>70547.12</v>
+        <v>308077.19</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>67706.73</v>
+        <v>297440.59</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>69376.42999999999</v>
+        <v>289896.9</v>
       </c>
       <c r="Y40" s="18" t="n">
-        <v>40936.31</v>
+        <v>278528.5</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>40936.31</v>
+        <v>278528.5</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>70632.41</v>
+        <v>286712.75</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>64760.48</v>
+        <v>286603.88</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -23079,49 +22863,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>유동리스부채</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="n"/>
+          <t>부채와자본총계</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>585743.67</v>
+      </c>
+      <c r="F41" s="37" t="n">
+        <v>585743.67</v>
+      </c>
       <c r="G41" s="18" t="n">
-        <v>1131.63</v>
-      </c>
-      <c r="K41" s="9" t="n"/>
+        <v>604762.97</v>
+      </c>
+      <c r="H41" s="18" t="n">
+        <v>616212.41</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>642298.72</v>
+      </c>
+      <c r="J41" s="18" t="n">
+        <v>650813.3199999999</v>
+      </c>
+      <c r="K41" s="37" t="n">
+        <v>650813.3199999999</v>
+      </c>
       <c r="L41" s="18" t="n">
-        <v>1182.66</v>
+        <v>673225.14</v>
+      </c>
+      <c r="M41" s="18" t="n">
+        <v>673567.4</v>
+      </c>
+      <c r="N41" s="18" t="n">
+        <v>681285.17</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>1071.03</v>
+        <v>667910.9</v>
       </c>
       <c r="P41" s="37" t="n">
-        <v>1071.03</v>
+        <v>667910.9</v>
+      </c>
+      <c r="Q41" s="18" t="n">
+        <v>662588.12</v>
+      </c>
+      <c r="R41" s="18" t="n">
+        <v>659710.17</v>
+      </c>
+      <c r="S41" s="18" t="n">
+        <v>654339.55</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>905.54</v>
+        <v>634160.67</v>
       </c>
       <c r="U41" s="37" t="n">
-        <v>905.54</v>
+        <v>634160.67</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>934.85</v>
+        <v>644560.14</v>
       </c>
       <c r="W41" s="18" t="n">
-        <v>1216.26</v>
+        <v>651209.76</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>1020.99</v>
+        <v>644038.27</v>
       </c>
       <c r="Y41" s="18" t="n">
-        <v>798.17</v>
+        <v>624424.39</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>798.17</v>
+        <v>624424.39</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>887.24</v>
+        <v>637032.77</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>1092.91</v>
+        <v>657051.08</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -23143,49 +22958,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>리스부채</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="n"/>
+          <t>지배주주지분</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>281955.19</v>
+      </c>
+      <c r="F42" s="37" t="n">
+        <v>281955.19</v>
+      </c>
       <c r="G42" s="18" t="n">
-        <v>7421.46</v>
-      </c>
-      <c r="K42" s="9" t="n"/>
+        <v>291204.18</v>
+      </c>
+      <c r="H42" s="18" t="n">
+        <v>298464.7</v>
+      </c>
+      <c r="I42" s="18" t="n">
+        <v>310362.82</v>
+      </c>
+      <c r="J42" s="18" t="n">
+        <v>306649.36</v>
+      </c>
+      <c r="K42" s="37" t="n">
+        <v>306649.36</v>
+      </c>
       <c r="L42" s="18" t="n">
-        <v>8548.42</v>
+        <v>309204.92</v>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>318079.75</v>
+      </c>
+      <c r="N42" s="18" t="n">
+        <v>328691.25</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>7959</v>
+        <v>324208.94</v>
       </c>
       <c r="P42" s="37" t="n">
-        <v>7959</v>
+        <v>324208.94</v>
+      </c>
+      <c r="Q42" s="18" t="n">
+        <v>322745.94</v>
+      </c>
+      <c r="R42" s="18" t="n">
+        <v>324306.26</v>
+      </c>
+      <c r="S42" s="18" t="n">
+        <v>315497.89</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>6244.93</v>
+        <v>312663.46</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>6244.93</v>
+        <v>312663.46</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>6098.61</v>
+        <v>308077.19</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>6077.98</v>
+        <v>297440.59</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>5739.46</v>
+        <v>289896.9</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>5389.7</v>
+        <v>278528.5</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>5389.7</v>
+        <v>278528.5</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>5353.17</v>
+        <v>286712.75</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>5441.83</v>
+        <v>286603.88</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -23207,49 +23053,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>단기금융부채</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="n"/>
+          <t>총차입금</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>229383.85</v>
+      </c>
+      <c r="F43" s="37" t="n">
+        <v>229383.85</v>
+      </c>
       <c r="G43" s="18" t="n">
-        <v>1131.63</v>
-      </c>
-      <c r="K43" s="9" t="n"/>
+        <v>236286.83</v>
+      </c>
+      <c r="H43" s="18" t="n">
+        <v>242543.35</v>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>258409.76</v>
+      </c>
+      <c r="J43" s="18" t="n">
+        <v>261895.27</v>
+      </c>
+      <c r="K43" s="37" t="n">
+        <v>261895.27</v>
+      </c>
       <c r="L43" s="18" t="n">
-        <v>1182.66</v>
+        <v>283555.55</v>
+      </c>
+      <c r="M43" s="18" t="n">
+        <v>265587.84</v>
+      </c>
+      <c r="N43" s="18" t="n">
+        <v>265501.6</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>1071.03</v>
+        <v>260770.73</v>
       </c>
       <c r="P43" s="37" t="n">
-        <v>1071.03</v>
+        <v>260770.73</v>
+      </c>
+      <c r="Q43" s="18" t="n">
+        <v>264285.82</v>
+      </c>
+      <c r="R43" s="18" t="n">
+        <v>266753.46</v>
+      </c>
+      <c r="S43" s="18" t="n">
+        <v>280337.48</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>905.54</v>
+        <v>263285.46</v>
       </c>
       <c r="U43" s="37" t="n">
-        <v>905.54</v>
+        <v>263285.46</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>934.85</v>
+        <v>273485.84</v>
       </c>
       <c r="W43" s="18" t="n">
-        <v>1216.26</v>
+        <v>281194.34</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>1020.99</v>
+        <v>278467.43</v>
       </c>
       <c r="Y43" s="18" t="n">
-        <v>798.17</v>
+        <v>280548.34</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>798.17</v>
+        <v>280548.34</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>887.24</v>
+        <v>280050.03</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>1092.91</v>
+        <v>301543.56</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -23271,49 +23148,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="n"/>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>173172.52</v>
+      </c>
+      <c r="F44" s="37" t="n">
+        <v>173172.52</v>
+      </c>
       <c r="G44" s="18" t="n">
-        <v>6289.83</v>
-      </c>
-      <c r="K44" s="9" t="n"/>
+        <v>173218.61</v>
+      </c>
+      <c r="H44" s="18" t="n">
+        <v>179986.32</v>
+      </c>
+      <c r="I44" s="18" t="n">
+        <v>201485.61</v>
+      </c>
+      <c r="J44" s="18" t="n">
+        <v>206412.87</v>
+      </c>
+      <c r="K44" s="37" t="n">
+        <v>206412.87</v>
+      </c>
       <c r="L44" s="18" t="n">
-        <v>7365.76</v>
+        <v>219494.66</v>
+      </c>
+      <c r="M44" s="18" t="n">
+        <v>199709.65</v>
+      </c>
+      <c r="N44" s="18" t="n">
+        <v>198184.34</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>6887.97</v>
+        <v>195656.66</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>6887.97</v>
+        <v>195656.66</v>
+      </c>
+      <c r="Q44" s="18" t="n">
+        <v>203333.87</v>
+      </c>
+      <c r="R44" s="18" t="n">
+        <v>231054.4</v>
+      </c>
+      <c r="S44" s="18" t="n">
+        <v>237837.33</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>5339.39</v>
+        <v>229665.39</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>5339.39</v>
+        <v>229665.39</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>5163.76</v>
+        <v>211007.49</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>4861.72</v>
+        <v>222097.3</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>4718.47</v>
+        <v>220079.87</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>4591.53</v>
+        <v>239612.03</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>4591.53</v>
+        <v>239612.03</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>4465.93</v>
+        <v>229154.31</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>4348.92</v>
+        <v>256040.64</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -23335,49 +23243,80 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>64324.31</v>
+      </c>
+      <c r="F45" s="37" t="n">
+        <v>64324.31</v>
+      </c>
       <c r="G45" s="18" t="n">
-        <v>6289.83</v>
-      </c>
-      <c r="K45" s="9" t="n"/>
+        <v>71906.63</v>
+      </c>
+      <c r="H45" s="18" t="n">
+        <v>70193.96000000001</v>
+      </c>
+      <c r="I45" s="18" t="n">
+        <v>78918.78999999999</v>
+      </c>
+      <c r="J45" s="18" t="n">
+        <v>77850.74000000001</v>
+      </c>
+      <c r="K45" s="37" t="n">
+        <v>77850.74000000001</v>
+      </c>
       <c r="L45" s="18" t="n">
-        <v>7365.76</v>
+        <v>86709.69</v>
+      </c>
+      <c r="M45" s="18" t="n">
+        <v>88666.45</v>
+      </c>
+      <c r="N45" s="18" t="n">
+        <v>84861.5</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>6887.97</v>
+        <v>84103.55</v>
       </c>
       <c r="P45" s="37" t="n">
-        <v>6887.97</v>
+        <v>84103.55</v>
+      </c>
+      <c r="Q45" s="18" t="n">
+        <v>79457.13</v>
+      </c>
+      <c r="R45" s="18" t="n">
+        <v>54018.87</v>
+      </c>
+      <c r="S45" s="18" t="n">
+        <v>61014.96</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>5339.39</v>
+        <v>41553.91</v>
       </c>
       <c r="U45" s="37" t="n">
-        <v>5339.39</v>
+        <v>41553.91</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>5163.76</v>
+        <v>70547.12</v>
       </c>
       <c r="W45" s="18" t="n">
-        <v>4861.72</v>
+        <v>67706.73</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>4718.47</v>
+        <v>69376.42999999999</v>
       </c>
       <c r="Y45" s="18" t="n">
-        <v>4591.53</v>
+        <v>40936.31</v>
       </c>
       <c r="Z45" s="37" t="n">
-        <v>4591.53</v>
+        <v>40936.31</v>
       </c>
       <c r="AA45" s="18" t="n">
-        <v>4465.93</v>
+        <v>70632.41</v>
       </c>
       <c r="AB45" s="19" t="n">
-        <v>4348.92</v>
+        <v>64760.48</v>
       </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
@@ -28946,11 +28885,11 @@
       <c r="AA12" s="18" t="n"/>
       <c r="AB12" s="19" t="n"/>
       <c r="AC12" s="20">
-        <f>IFERROR((AB28*변수!$D$54-AB26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AB28*변수!$D$53-AB26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC28*변수!$D$54-AC26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AC28*변수!$D$53-AC26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -28958,19 +28897,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD28*변수!$D$54-AD26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AD28*변수!$D$53-AD26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF28*변수!$D$54-AF26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AF28*변수!$D$53-AF26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG28*변수!$D$54-AG26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AG28*변수!$D$53-AG26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH28*변수!$D$54-AH26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AH28*변수!$D$53-AH26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -28978,19 +28917,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI28*변수!$D$54-AI26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AI28*변수!$D$53-AI26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK28*변수!$D$54-AK26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AK28*변수!$D$53-AK26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL28*변수!$D$54-AL26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AL28*변수!$D$53-AL26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM28*변수!$D$54-AM26*변수!$D$55)/4,"")</f>
+        <f>IFERROR((AM28*변수!$D$53-AM26*변수!$D$54)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -32368,86 +32307,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E34" s="18" t="n">
-        <v>198.7</v>
+      <c r="E34" s="18">
+        <f>IFERROR(E33,"")</f>
+        <v/>
       </c>
       <c r="F34" s="37" t="n"/>
-      <c r="G34" s="18" t="n">
-        <v>344.4</v>
-      </c>
-      <c r="H34" s="18" t="n">
-        <v>215.2</v>
-      </c>
-      <c r="I34" s="18" t="n">
-        <v>1435</v>
-      </c>
-      <c r="J34" s="18" t="n">
-        <v>-99.90000000000001</v>
+      <c r="G34" s="18">
+        <f>IFERROR(G33,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="18">
+        <f>IFERROR(H33,"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="18">
+        <f>IFERROR(I33,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="18">
+        <f>IFERROR(J33,"")</f>
+        <v/>
       </c>
       <c r="K34" s="37">
         <f>SUM(G34:J34)</f>
         <v/>
       </c>
-      <c r="L34" s="18" t="n">
-        <v>285.3</v>
-      </c>
-      <c r="M34" s="18" t="n">
-        <v>430.4</v>
-      </c>
-      <c r="N34" s="18" t="n">
-        <v>519.4</v>
-      </c>
-      <c r="O34" s="18" t="n">
-        <v>193.3</v>
+      <c r="L34" s="18">
+        <f>IFERROR(L33,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="18">
+        <f>IFERROR(M33,"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="18">
+        <f>IFERROR(N33,"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="18">
+        <f>IFERROR(O33,"")</f>
+        <v/>
       </c>
       <c r="P34" s="37">
         <f>SUM(L34:O34)</f>
         <v/>
       </c>
-      <c r="Q34" s="18" t="n">
-        <v>233.6</v>
-      </c>
-      <c r="R34" s="18" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="S34" s="18" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="T34" s="18" t="n">
-        <v>-101.1</v>
+      <c r="Q34" s="18">
+        <f>IFERROR(Q33,"")</f>
+        <v/>
+      </c>
+      <c r="R34" s="18">
+        <f>IFERROR(R33,"")</f>
+        <v/>
+      </c>
+      <c r="S34" s="18">
+        <f>IFERROR(S33,"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="18">
+        <f>IFERROR(T33,"")</f>
+        <v/>
       </c>
       <c r="U34" s="37">
         <f>SUM(Q34:T34)</f>
         <v/>
       </c>
-      <c r="V34" s="18" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="W34" s="18" t="n">
-        <v>-228.1</v>
-      </c>
-      <c r="X34" s="18" t="n">
-        <v>-292.5</v>
-      </c>
-      <c r="Y34" s="20" t="n">
-        <v>-338.5</v>
+      <c r="V34" s="18">
+        <f>IFERROR(V33,"")</f>
+        <v/>
+      </c>
+      <c r="W34" s="18">
+        <f>IFERROR(W33,"")</f>
+        <v/>
+      </c>
+      <c r="X34" s="18">
+        <f>IFERROR(X33,"")</f>
+        <v/>
+      </c>
+      <c r="Y34" s="20">
+        <f>IFERROR((Y18-(-214.18)*(1.0))*100/Y32,"")</f>
+        <v/>
       </c>
       <c r="Z34" s="37">
         <f>SUM(V34:Y34)</f>
         <v/>
       </c>
-      <c r="AA34" s="18" t="n">
-        <v>503.3</v>
-      </c>
-      <c r="AB34" s="19" t="n">
-        <v>256.6</v>
+      <c r="AA34" s="18">
+        <f>IFERROR(AA33,"")</f>
+        <v/>
+      </c>
+      <c r="AB34" s="19">
+        <f>IFERROR(AB33,"")</f>
+        <v/>
       </c>
       <c r="AC34" s="20">
-        <f>IFERROR(X34*(1+변수!AC40),"")</f>
+        <f>IFERROR(AC33,"")</f>
         <v/>
       </c>
       <c r="AD34" s="20">
-        <f>IFERROR(Y34*(1+변수!AD40),"")</f>
+        <f>IFERROR(AD33,"")</f>
         <v/>
       </c>
       <c r="AE34" s="38">
@@ -32455,19 +32413,19 @@
         <v/>
       </c>
       <c r="AF34" s="20">
-        <f>IFERROR(AA34*(1+변수!AF40),"")</f>
+        <f>IFERROR(AF33,"")</f>
         <v/>
       </c>
       <c r="AG34" s="20">
-        <f>IFERROR(AB34*(1+변수!AG40),"")</f>
+        <f>IFERROR(AG33,"")</f>
         <v/>
       </c>
       <c r="AH34" s="20">
-        <f>IFERROR(AC34*(1+변수!AH40),"")</f>
+        <f>IFERROR(AH33,"")</f>
         <v/>
       </c>
       <c r="AI34" s="20">
-        <f>IFERROR(AD34*(1+변수!AI40),"")</f>
+        <f>IFERROR(AI33,"")</f>
         <v/>
       </c>
       <c r="AJ34" s="38">
@@ -32475,19 +32433,19 @@
         <v/>
       </c>
       <c r="AK34" s="20">
-        <f>IFERROR(AF34*(1+변수!AK40),"")</f>
+        <f>IFERROR(AK33,"")</f>
         <v/>
       </c>
       <c r="AL34" s="20">
-        <f>IFERROR(AG34*(1+변수!AL40),"")</f>
+        <f>IFERROR(AL33,"")</f>
         <v/>
       </c>
       <c r="AM34" s="20">
-        <f>IFERROR(AH34*(1+변수!AM40),"")</f>
+        <f>IFERROR(AM33,"")</f>
         <v/>
       </c>
       <c r="AN34" s="20">
-        <f>IFERROR(AI34*(1+변수!AN40),"")</f>
+        <f>IFERROR(AN33,"")</f>
         <v/>
       </c>
       <c r="AO34" s="38">
@@ -32736,7 +32694,7 @@
       <c r="AB36" s="19" t="n"/>
       <c r="AC36" s="20" t="n"/>
       <c r="AD36" s="20">
-        <f>변수!AD41</f>
+        <f>변수!AD40</f>
         <v/>
       </c>
       <c r="AE36" s="38">
@@ -32747,7 +32705,7 @@
       <c r="AG36" s="20" t="n"/>
       <c r="AH36" s="20" t="n"/>
       <c r="AI36" s="20">
-        <f>변수!AI41</f>
+        <f>변수!AI40</f>
         <v/>
       </c>
       <c r="AJ36" s="38">
@@ -32758,7 +32716,7 @@
       <c r="AL36" s="20" t="n"/>
       <c r="AM36" s="20" t="n"/>
       <c r="AN36" s="20">
-        <f>변수!AN41</f>
+        <f>변수!AN40</f>
         <v/>
       </c>
       <c r="AO36" s="38">
@@ -32858,7 +32816,7 @@
       <c r="AB37" s="15" t="n"/>
       <c r="AC37" s="39" t="n"/>
       <c r="AD37" s="39">
-        <f>IFERROR(변수!$D$44/(AA33+AB33+AC33+AD33),"")</f>
+        <f>IFERROR(변수!$D$43/(AA33+AB33+AC33+AD33),"")</f>
         <v/>
       </c>
       <c r="AE37" s="40">
@@ -32866,19 +32824,19 @@
         <v/>
       </c>
       <c r="AF37" s="39">
-        <f>IFERROR(변수!$D$44/(AB33+AC33+AD33+AF33),"")</f>
+        <f>IFERROR(변수!$D$43/(AB33+AC33+AD33+AF33),"")</f>
         <v/>
       </c>
       <c r="AG37" s="39">
-        <f>IFERROR(변수!$D$44/(AC33+AD33+AF33+AG33),"")</f>
+        <f>IFERROR(변수!$D$43/(AC33+AD33+AF33+AG33),"")</f>
         <v/>
       </c>
       <c r="AH37" s="39">
-        <f>IFERROR(변수!$D$44/(AD33+AF33+AG33+AH33),"")</f>
+        <f>IFERROR(변수!$D$43/(AD33+AF33+AG33+AH33),"")</f>
         <v/>
       </c>
       <c r="AI37" s="39">
-        <f>IFERROR(변수!$D$44/(AF33+AG33+AH33+AI33),"")</f>
+        <f>IFERROR(변수!$D$43/(AF33+AG33+AH33+AI33),"")</f>
         <v/>
       </c>
       <c r="AJ37" s="40">
@@ -32886,19 +32844,19 @@
         <v/>
       </c>
       <c r="AK37" s="39">
-        <f>IFERROR(변수!$D$44/(AG33+AH33+AI33+AK33),"")</f>
+        <f>IFERROR(변수!$D$43/(AG33+AH33+AI33+AK33),"")</f>
         <v/>
       </c>
       <c r="AL37" s="39">
-        <f>IFERROR(변수!$D$44/(AH33+AI33+AK33+AL33),"")</f>
+        <f>IFERROR(변수!$D$43/(AH33+AI33+AK33+AL33),"")</f>
         <v/>
       </c>
       <c r="AM37" s="39">
-        <f>IFERROR(변수!$D$44/(AI33+AK33+AL33+AM33),"")</f>
+        <f>IFERROR(변수!$D$43/(AI33+AK33+AL33+AM33),"")</f>
         <v/>
       </c>
       <c r="AN37" s="39">
-        <f>IFERROR(변수!$D$44/(AK33+AL33+AM33+AN33),"")</f>
+        <f>IFERROR(변수!$D$43/(AK33+AL33+AM33+AN33),"")</f>
         <v/>
       </c>
       <c r="AO37" s="40">
@@ -33024,11 +32982,11 @@
         <v/>
       </c>
       <c r="AC38" s="39">
-        <f>IFERROR(변수!$D$44/AC35,"")</f>
+        <f>IFERROR(변수!$D$43/AC35,"")</f>
         <v/>
       </c>
       <c r="AD38" s="39">
-        <f>IFERROR(변수!$D$44/AD35,"")</f>
+        <f>IFERROR(변수!$D$43/AD35,"")</f>
         <v/>
       </c>
       <c r="AE38" s="40">
@@ -33036,19 +32994,19 @@
         <v/>
       </c>
       <c r="AF38" s="39">
-        <f>IFERROR(변수!$D$44/AF35,"")</f>
+        <f>IFERROR(변수!$D$43/AF35,"")</f>
         <v/>
       </c>
       <c r="AG38" s="39">
-        <f>IFERROR(변수!$D$44/AG35,"")</f>
+        <f>IFERROR(변수!$D$43/AG35,"")</f>
         <v/>
       </c>
       <c r="AH38" s="39">
-        <f>IFERROR(변수!$D$44/AH35,"")</f>
+        <f>IFERROR(변수!$D$43/AH35,"")</f>
         <v/>
       </c>
       <c r="AI38" s="39">
-        <f>IFERROR(변수!$D$44/AI35,"")</f>
+        <f>IFERROR(변수!$D$43/AI35,"")</f>
         <v/>
       </c>
       <c r="AJ38" s="40">
@@ -33056,19 +33014,19 @@
         <v/>
       </c>
       <c r="AK38" s="39">
-        <f>IFERROR(변수!$D$44/AK35,"")</f>
+        <f>IFERROR(변수!$D$43/AK35,"")</f>
         <v/>
       </c>
       <c r="AL38" s="39">
-        <f>IFERROR(변수!$D$44/AL35,"")</f>
+        <f>IFERROR(변수!$D$43/AL35,"")</f>
         <v/>
       </c>
       <c r="AM38" s="39">
-        <f>IFERROR(변수!$D$44/AM35,"")</f>
+        <f>IFERROR(변수!$D$43/AM35,"")</f>
         <v/>
       </c>
       <c r="AN38" s="39">
-        <f>IFERROR(변수!$D$44/AN35,"")</f>
+        <f>IFERROR(변수!$D$43/AN35,"")</f>
         <v/>
       </c>
       <c r="AO38" s="40">
@@ -34102,7 +34060,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
       <c r="W2" s="42" t="n"/>
@@ -39491,7 +39449,7 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
       <c r="I2" s="42" t="n"/>
@@ -41346,7 +41304,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D44</f>
+        <f>변수!D43</f>
         <v/>
       </c>
     </row>
@@ -41357,7 +41315,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D45</f>
+        <f>변수!D44</f>
         <v/>
       </c>
     </row>
@@ -41534,7 +41492,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D50+F7*(1-변수!D50),"")</f>
+        <f>IFERROR(E7*변수!D49+F7*(1-변수!D49),"")</f>
         <v/>
       </c>
     </row>
@@ -41545,7 +41503,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -41569,7 +41527,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -41593,7 +41551,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D49</f>
+        <f>변수!D48</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -41657,7 +41615,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -43468,7 +43426,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D57</f>
+        <f>변수!D56</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5176,35 +5176,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6144,7 +6144,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4600</v>
+        <v>4580</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6417,7 +6417,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4603</v>
+        <v>4599</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9279,11 +9279,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>4600</v>
+        <v>4580</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,565원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,595원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9671,7 +9671,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.02463660282729904</v>
+        <v>0.02463660282730479</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03995916337487649</v>
+        <v>0.03995916337487803</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -41690,7 +41690,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.17</v>
+        <v>28.05</v>
       </c>
     </row>
     <row r="32">
@@ -41700,7 +41700,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="33">
@@ -41740,7 +41740,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.88</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4298,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4298,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4298,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4580</v>
+        <v>4400</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>3420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4375</v>
+        <v>4325</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6417,7 +6417,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4599</v>
+        <v>4565.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>4580</v>
+        <v>4400</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39462,7 +39462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41690,7 +41690,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.05</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="32">
@@ -41700,7 +41700,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="33">
@@ -41740,7 +41740,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.87</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4298,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6144,7 +6144,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4400</v>
+        <v>4410</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>3420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4325</v>
+        <v>4250</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6417,7 +6417,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4565.8</v>
+        <v>4539.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9279,11 +9279,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>4400</v>
+        <v>4410</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,595원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,605원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39462,7 +39462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41690,7 +41690,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.94</v>
+        <v>27.01</v>
       </c>
     </row>
     <row r="32">
@@ -41740,7 +41740,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.81</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4298,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6144,7 +6144,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4410</v>
+        <v>4435</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6417,7 +6417,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4539.3</v>
+        <v>4523.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9279,11 +9279,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>4410</v>
+        <v>4435</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,605원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,415원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39462,7 +39462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41690,7 +41690,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.01</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="32">
@@ -41740,7 +41740,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.82</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4298,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6144,7 +6144,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4435</v>
+        <v>4420</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>3420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4250</v>
+        <v>4140</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6417,7 +6417,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4523.8</v>
+        <v>4459.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9279,11 +9279,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>4435</v>
+        <v>4420</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,415원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,255원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39462,7 +39462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41690,7 +41690,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.16</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="32">
@@ -41740,7 +41740,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.83</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="37">

--- a/argus/kship/models/014280_model.xlsx
+++ b/argus/kship/models/014280_model.xlsx
@@ -4298,7 +4298,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5176,35 +5176,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5295,35 +5295,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5414,35 +5414,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5533,35 +5533,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5652,35 +5652,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5771,35 +5771,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5890,35 +5890,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6009,35 +6009,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6144,7 +6144,7 @@
         <v>4850</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4420</v>
+        <v>4015</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6326,7 +6326,7 @@
         <v>3420</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4140</v>
+        <v>3940</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6417,7 +6417,7 @@
         <v>4234.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4459.1</v>
+        <v>4361.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9279,11 +9279,11 @@
         </is>
       </c>
       <c r="D43" s="34" t="n">
-        <v>4420</v>
+        <v>4015</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,255원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,220원)</t>
         </is>
       </c>
       <c r="F43" s="9" t="n"/>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="D44" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19221,7 +19221,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34073,7 +34073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39462,7 +39462,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41690,7 +41690,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.07</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="32">
@@ -41700,7 +41700,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
@@ -41740,7 +41740,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.82</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="37">
